--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -4977,10 +4977,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121093817</v>
+        <v>121091232</v>
       </c>
       <c r="B39" t="n">
-        <v>5169</v>
+        <v>90687</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4989,46 +4989,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696239</v>
+        <v>696101</v>
       </c>
       <c r="R39" t="n">
-        <v>6603315</v>
+        <v>6603200</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5055,19 +5050,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5082,22 +5067,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121091232</v>
+        <v>121095556</v>
       </c>
       <c r="B40" t="n">
-        <v>90687</v>
+        <v>57364</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5110,34 +5095,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696101</v>
+        <v>695980</v>
       </c>
       <c r="R40" t="n">
-        <v>6603200</v>
+        <v>6603096</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5308,10 +5298,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121095556</v>
+        <v>121093817</v>
       </c>
       <c r="B42" t="n">
-        <v>57364</v>
+        <v>5169</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5320,31 +5310,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5353,13 +5343,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695980</v>
+        <v>696239</v>
       </c>
       <c r="R42" t="n">
-        <v>6603096</v>
+        <v>6603315</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5386,9 +5376,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5403,12 +5403,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121093800</v>
+        <v>121090597</v>
       </c>
       <c r="B48" t="n">
-        <v>57364</v>
+        <v>94690</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5987,46 +5987,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696239</v>
+        <v>695897</v>
       </c>
       <c r="R48" t="n">
-        <v>6603325</v>
+        <v>6603417</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6065,7 +6060,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,10 +6087,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121090597</v>
+        <v>121093800</v>
       </c>
       <c r="B49" t="n">
-        <v>94690</v>
+        <v>57364</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6104,41 +6099,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695897</v>
+        <v>696239</v>
       </c>
       <c r="R49" t="n">
-        <v>6603417</v>
+        <v>6603325</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7237,10 +7237,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121095125</v>
+        <v>121090488</v>
       </c>
       <c r="B59" t="n">
-        <v>100337</v>
+        <v>79583</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7253,37 +7253,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696122</v>
+        <v>695888</v>
       </c>
       <c r="R59" t="n">
-        <v>6603202</v>
+        <v>6603408</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7310,11 +7310,21 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7323,23 +7333,43 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121093980</v>
+        <v>121095125</v>
       </c>
       <c r="B60" t="n">
         <v>100337</v>
@@ -7379,10 +7409,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696434</v>
+        <v>696122</v>
       </c>
       <c r="R60" t="n">
-        <v>6603315</v>
+        <v>6603202</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7441,10 +7471,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121090488</v>
+        <v>121093980</v>
       </c>
       <c r="B61" t="n">
-        <v>79583</v>
+        <v>100337</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7457,37 +7487,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695888</v>
+        <v>696434</v>
       </c>
       <c r="R61" t="n">
-        <v>6603408</v>
+        <v>6603315</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7514,21 +7544,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7537,36 +7557,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4865,10 +4865,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121095265</v>
+        <v>121091186</v>
       </c>
       <c r="B38" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696112</v>
+        <v>696070</v>
       </c>
       <c r="R38" t="n">
-        <v>6603209</v>
+        <v>6603197</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4977,10 +4977,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121091232</v>
+        <v>121090637</v>
       </c>
       <c r="B39" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4989,38 +4989,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696101</v>
+        <v>695859</v>
       </c>
       <c r="R39" t="n">
-        <v>6603200</v>
+        <v>6603407</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5079,10 +5079,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121095556</v>
+        <v>121095265</v>
       </c>
       <c r="B40" t="n">
-        <v>57364</v>
+        <v>90697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5095,42 +5095,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695980</v>
+        <v>696112</v>
       </c>
       <c r="R40" t="n">
-        <v>6603096</v>
+        <v>6603209</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,9 +5152,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5174,22 +5179,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121091050</v>
+        <v>121090488</v>
       </c>
       <c r="B41" t="n">
-        <v>8421</v>
+        <v>79586</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5202,46 +5207,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695927</v>
+        <v>695888</v>
       </c>
       <c r="R41" t="n">
-        <v>6603231</v>
+        <v>6603408</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5268,40 +5264,69 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121093817</v>
+        <v>121090372</v>
       </c>
       <c r="B42" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5310,43 +5335,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696239</v>
+        <v>695883</v>
       </c>
       <c r="R42" t="n">
-        <v>6603315</v>
+        <v>6603408</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5378,7 +5398,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5388,7 +5408,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5415,10 +5435,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121090637</v>
+        <v>121091232</v>
       </c>
       <c r="B43" t="n">
-        <v>100337</v>
+        <v>90697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5427,38 +5447,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695859</v>
+        <v>696101</v>
       </c>
       <c r="R43" t="n">
-        <v>6603407</v>
+        <v>6603200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5517,14 +5537,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121090764</v>
+        <v>121095837</v>
       </c>
       <c r="B44" t="n">
-        <v>94474</v>
+        <v>5189</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5533,37 +5553,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2809</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695871</v>
+        <v>695989</v>
       </c>
       <c r="R44" t="n">
-        <v>6603412</v>
+        <v>6603160</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5592,7 +5617,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5602,12 +5627,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5634,10 +5654,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121091319</v>
+        <v>121090442</v>
       </c>
       <c r="B45" t="n">
-        <v>78598</v>
+        <v>79586</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5646,41 +5666,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696097</v>
+        <v>695921</v>
       </c>
       <c r="R45" t="n">
-        <v>6603185</v>
+        <v>6603409</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5707,19 +5727,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5734,22 +5744,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121091126</v>
+        <v>121090910</v>
       </c>
       <c r="B46" t="n">
-        <v>78598</v>
+        <v>100347</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5758,41 +5768,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696034</v>
+        <v>695893</v>
       </c>
       <c r="R46" t="n">
-        <v>6603209</v>
+        <v>6603281</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,19 +5829,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5846,22 +5846,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121095299</v>
+        <v>121093980</v>
       </c>
       <c r="B47" t="n">
-        <v>5169</v>
+        <v>100347</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5874,42 +5874,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696094</v>
+        <v>696434</v>
       </c>
       <c r="R47" t="n">
-        <v>6603186</v>
+        <v>6603315</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5936,19 +5931,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5963,22 +5948,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121090597</v>
+        <v>121095556</v>
       </c>
       <c r="B48" t="n">
-        <v>94690</v>
+        <v>57367</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5987,41 +5972,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695897</v>
+        <v>695980</v>
       </c>
       <c r="R48" t="n">
-        <v>6603417</v>
+        <v>6603096</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6048,19 +6038,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6075,70 +6055,65 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121093800</v>
+        <v>121090764</v>
       </c>
       <c r="B49" t="n">
-        <v>57364</v>
+        <v>94484</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696239</v>
+        <v>695871</v>
       </c>
       <c r="R49" t="n">
-        <v>6603325</v>
+        <v>6603412</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6167,7 +6142,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6177,7 +6152,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,10 +6184,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121093815</v>
+        <v>121091126</v>
       </c>
       <c r="B50" t="n">
-        <v>5189</v>
+        <v>78601</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6216,43 +6196,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696247</v>
+        <v>696034</v>
       </c>
       <c r="R50" t="n">
-        <v>6603313</v>
+        <v>6603209</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6284,7 +6259,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6294,7 +6269,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6321,10 +6296,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121095510</v>
+        <v>121094501</v>
       </c>
       <c r="B51" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6337,21 +6312,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6362,14 +6337,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696021</v>
+        <v>696380</v>
       </c>
       <c r="R51" t="n">
-        <v>6603152</v>
+        <v>6603325</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6401,7 +6376,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6411,7 +6386,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6438,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121092954</v>
+        <v>121099960</v>
       </c>
       <c r="B52" t="n">
-        <v>94737</v>
+        <v>91156</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6450,41 +6425,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2170</v>
+        <v>5467</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696174</v>
+        <v>695863</v>
       </c>
       <c r="R52" t="n">
-        <v>6603210</v>
+        <v>6603398</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6508,22 +6483,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6534,6 +6514,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121090910</v>
+        <v>121095299</v>
       </c>
       <c r="B53" t="n">
-        <v>100337</v>
+        <v>5169</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6566,37 +6566,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695893</v>
+        <v>696094</v>
       </c>
       <c r="R53" t="n">
-        <v>6603281</v>
+        <v>6603186</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6623,9 +6628,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6640,22 +6655,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121090372</v>
+        <v>121091319</v>
       </c>
       <c r="B54" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6668,21 +6683,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6692,10 +6707,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>695883</v>
+        <v>696097</v>
       </c>
       <c r="R54" t="n">
-        <v>6603408</v>
+        <v>6603185</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6727,7 +6742,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6737,7 +6752,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6764,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121094501</v>
+        <v>121093973</v>
       </c>
       <c r="B55" t="n">
-        <v>5169</v>
+        <v>91985</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6780,42 +6795,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696380</v>
+        <v>696429</v>
       </c>
       <c r="R55" t="n">
-        <v>6603325</v>
+        <v>6603315</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6842,19 +6852,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6869,22 +6869,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121099960</v>
+        <v>121093800</v>
       </c>
       <c r="B56" t="n">
-        <v>91146</v>
+        <v>57367</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,37 +6897,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>695863</v>
+        <v>696239</v>
       </c>
       <c r="R56" t="n">
-        <v>6603398</v>
+        <v>6603325</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6951,27 +6956,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6982,26 +6982,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7018,10 +6998,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121094438</v>
+        <v>121092954</v>
       </c>
       <c r="B57" t="n">
-        <v>5169</v>
+        <v>94747</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7034,42 +7014,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696484</v>
+        <v>696174</v>
       </c>
       <c r="R57" t="n">
-        <v>6603311</v>
+        <v>6603210</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7098,7 +7073,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7108,7 +7083,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7138,7 +7113,7 @@
         <v>121091204</v>
       </c>
       <c r="B58" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7237,10 +7212,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121090488</v>
+        <v>121090597</v>
       </c>
       <c r="B59" t="n">
-        <v>79583</v>
+        <v>94700</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7253,21 +7228,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>210</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7277,10 +7252,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695888</v>
+        <v>695897</v>
       </c>
       <c r="R59" t="n">
-        <v>6603408</v>
+        <v>6603417</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7312,7 +7287,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7322,7 +7297,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7333,26 +7308,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7369,10 +7324,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121095125</v>
+        <v>121091050</v>
       </c>
       <c r="B60" t="n">
-        <v>100337</v>
+        <v>8421</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7385,34 +7340,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696122</v>
+        <v>695927</v>
       </c>
       <c r="R60" t="n">
-        <v>6603202</v>
+        <v>6603231</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7453,6 +7417,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7471,10 +7436,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121093980</v>
+        <v>121093815</v>
       </c>
       <c r="B61" t="n">
-        <v>100337</v>
+        <v>5189</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7487,37 +7452,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696434</v>
+        <v>696247</v>
       </c>
       <c r="R61" t="n">
-        <v>6603315</v>
+        <v>6603313</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7544,9 +7514,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7561,22 +7541,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121093973</v>
+        <v>121095510</v>
       </c>
       <c r="B62" t="n">
-        <v>91975</v>
+        <v>5189</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7589,37 +7569,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696429</v>
+        <v>696021</v>
       </c>
       <c r="R62" t="n">
-        <v>6603315</v>
+        <v>6603152</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7646,9 +7631,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7663,22 +7658,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121095837</v>
+        <v>121094438</v>
       </c>
       <c r="B63" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7691,21 +7686,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7716,14 +7711,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>695989</v>
+        <v>696484</v>
       </c>
       <c r="R63" t="n">
-        <v>6603160</v>
+        <v>6603311</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7755,7 +7750,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7765,7 +7760,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7792,10 +7787,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121091186</v>
+        <v>121095125</v>
       </c>
       <c r="B64" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7804,41 +7799,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696070</v>
+        <v>696122</v>
       </c>
       <c r="R64" t="n">
-        <v>6603197</v>
+        <v>6603202</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7865,19 +7860,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7892,22 +7877,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121090442</v>
+        <v>121090573</v>
       </c>
       <c r="B65" t="n">
-        <v>79583</v>
+        <v>94700</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7920,34 +7905,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>210</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695921</v>
+        <v>695901</v>
       </c>
       <c r="R65" t="n">
-        <v>6603409</v>
+        <v>6603407</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8006,10 +8000,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121090573</v>
+        <v>121093817</v>
       </c>
       <c r="B66" t="n">
-        <v>94690</v>
+        <v>5169</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8022,46 +8016,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>695901</v>
+        <v>696239</v>
       </c>
       <c r="R66" t="n">
-        <v>6603407</v>
+        <v>6603315</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8088,9 +8078,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8105,12 +8105,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8120,7 +8120,7 @@
         <v>121090765</v>
       </c>
       <c r="B67" t="n">
-        <v>94474</v>
+        <v>94484</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8216,6 +8216,2282 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121404815</v>
+      </c>
+      <c r="B68" t="n">
+        <v>94484</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>695864</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6603266</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121402388</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>695971</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6603090</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>121404558</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>695865</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6603318</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>121402709</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>696025</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6603166</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121405386</v>
+      </c>
+      <c r="B72" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>696099</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6603163</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>121402355</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>696001</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6603109</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>121404366</v>
+      </c>
+      <c r="B74" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>695857</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6603366</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>121404209</v>
+      </c>
+      <c r="B75" t="n">
+        <v>94484</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>695935</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6603415</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121404249</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>695896</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6603382</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121402809</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>696135</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6603162</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121402352</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>696013</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6603120</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121404293</v>
+      </c>
+      <c r="B79" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>695856</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6603367</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121402404</v>
+      </c>
+      <c r="B80" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>695942</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6603075</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121404898</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>696024</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6603210</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121404539</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>695869</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6603281</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>121404569</v>
+      </c>
+      <c r="B83" t="n">
+        <v>4772</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>695858</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6603299</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>121403961</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79682</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>695886</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6603243</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>121404545</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>695870</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6603295</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121405694</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>695999</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6603117</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121402402</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Tärnan, Tärnan, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>695942</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6603075</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121402734</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Torpängen, Torpängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>696145</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6603212</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -4977,10 +4977,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121090637</v>
+        <v>121095265</v>
       </c>
       <c r="B39" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4989,41 +4989,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695859</v>
+        <v>696112</v>
       </c>
       <c r="R39" t="n">
-        <v>6603407</v>
+        <v>6603209</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5050,9 +5050,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5067,22 +5077,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121095265</v>
+        <v>121090637</v>
       </c>
       <c r="B40" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5091,41 +5101,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696112</v>
+        <v>695859</v>
       </c>
       <c r="R40" t="n">
-        <v>6603209</v>
+        <v>6603407</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5152,19 +5162,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5179,12 +5179,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121091232</v>
+        <v>121090442</v>
       </c>
       <c r="B43" t="n">
-        <v>90697</v>
+        <v>79586</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5447,38 +5447,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696101</v>
+        <v>695921</v>
       </c>
       <c r="R43" t="n">
-        <v>6603200</v>
+        <v>6603409</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121090442</v>
+        <v>121091232</v>
       </c>
       <c r="B45" t="n">
-        <v>79586</v>
+        <v>90697</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5666,38 +5666,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695921</v>
+        <v>696101</v>
       </c>
       <c r="R45" t="n">
-        <v>6603409</v>
+        <v>6603200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -10038,10 +10038,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404545</v>
+        <v>121405694</v>
       </c>
       <c r="B85" t="n">
-        <v>8432</v>
+        <v>98081</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10050,38 +10050,52 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695870</v>
+        <v>695999</v>
       </c>
       <c r="R85" t="n">
-        <v>6603295</v>
+        <v>6603117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10111,9 +10125,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10128,22 +10157,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121405694</v>
+        <v>121404545</v>
       </c>
       <c r="B86" t="n">
-        <v>98081</v>
+        <v>8432</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10152,52 +10181,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695999</v>
+        <v>695870</v>
       </c>
       <c r="R86" t="n">
-        <v>6603117</v>
+        <v>6603295</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10227,24 +10242,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10259,12 +10259,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -4977,10 +4977,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121095265</v>
+        <v>121090637</v>
       </c>
       <c r="B39" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4989,41 +4989,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696112</v>
+        <v>695859</v>
       </c>
       <c r="R39" t="n">
-        <v>6603209</v>
+        <v>6603407</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5050,19 +5050,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5077,22 +5067,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121090637</v>
+        <v>121095265</v>
       </c>
       <c r="B40" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5101,41 +5091,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695859</v>
+        <v>696112</v>
       </c>
       <c r="R40" t="n">
-        <v>6603407</v>
+        <v>6603209</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5162,9 +5152,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5179,12 +5179,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121090442</v>
+        <v>121091232</v>
       </c>
       <c r="B43" t="n">
-        <v>79586</v>
+        <v>90697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5447,38 +5447,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695921</v>
+        <v>696101</v>
       </c>
       <c r="R43" t="n">
-        <v>6603409</v>
+        <v>6603200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121091232</v>
+        <v>121090442</v>
       </c>
       <c r="B45" t="n">
-        <v>90697</v>
+        <v>79586</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5666,38 +5666,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696101</v>
+        <v>695921</v>
       </c>
       <c r="R45" t="n">
-        <v>6603200</v>
+        <v>6603409</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -4865,10 +4865,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121091186</v>
+        <v>121090573</v>
       </c>
       <c r="B38" t="n">
-        <v>90697</v>
+        <v>94700</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4877,41 +4877,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696070</v>
+        <v>695901</v>
       </c>
       <c r="R38" t="n">
-        <v>6603197</v>
+        <v>6603407</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4938,19 +4947,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4965,22 +4964,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121090637</v>
+        <v>121091232</v>
       </c>
       <c r="B39" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4989,38 +4988,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695859</v>
+        <v>696101</v>
       </c>
       <c r="R39" t="n">
-        <v>6603407</v>
+        <v>6603200</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5079,7 +5078,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121095265</v>
+        <v>121091186</v>
       </c>
       <c r="B40" t="n">
         <v>90697</v>
@@ -5119,10 +5118,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696112</v>
+        <v>696070</v>
       </c>
       <c r="R40" t="n">
-        <v>6603209</v>
+        <v>6603197</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5154,7 +5153,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5164,7 +5163,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5191,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121090488</v>
+        <v>121090372</v>
       </c>
       <c r="B41" t="n">
-        <v>79586</v>
+        <v>90697</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5203,25 +5202,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5231,7 +5230,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695888</v>
+        <v>695883</v>
       </c>
       <c r="R41" t="n">
         <v>6603408</v>
@@ -5266,7 +5265,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5276,7 +5275,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5287,26 +5286,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5323,10 +5302,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121090372</v>
+        <v>121095556</v>
       </c>
       <c r="B42" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5339,37 +5318,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695883</v>
+        <v>695980</v>
       </c>
       <c r="R42" t="n">
-        <v>6603408</v>
+        <v>6603096</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5396,19 +5380,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,22 +5397,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121091232</v>
+        <v>121093817</v>
       </c>
       <c r="B43" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5447,41 +5421,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696101</v>
+        <v>696239</v>
       </c>
       <c r="R43" t="n">
-        <v>6603200</v>
+        <v>6603315</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5508,9 +5487,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5525,12 +5514,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5654,10 +5643,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121090442</v>
+        <v>121091126</v>
       </c>
       <c r="B45" t="n">
-        <v>79586</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5666,41 +5655,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695921</v>
+        <v>696034</v>
       </c>
       <c r="R45" t="n">
-        <v>6603409</v>
+        <v>6603209</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5727,9 +5716,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5744,22 +5743,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121090910</v>
+        <v>121091319</v>
       </c>
       <c r="B46" t="n">
-        <v>100347</v>
+        <v>78601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5768,41 +5767,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695893</v>
+        <v>696097</v>
       </c>
       <c r="R46" t="n">
-        <v>6603281</v>
+        <v>6603185</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5829,9 +5828,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5846,22 +5855,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121093980</v>
+        <v>121095299</v>
       </c>
       <c r="B47" t="n">
-        <v>100347</v>
+        <v>5169</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5874,37 +5883,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696434</v>
+        <v>696094</v>
       </c>
       <c r="R47" t="n">
-        <v>6603315</v>
+        <v>6603186</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5931,9 +5945,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5948,22 +5972,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121095556</v>
+        <v>121095510</v>
       </c>
       <c r="B48" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5972,20 +5996,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5996,22 +6020,22 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695980</v>
+        <v>696021</v>
       </c>
       <c r="R48" t="n">
-        <v>6603096</v>
+        <v>6603152</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6038,9 +6062,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6055,65 +6089,70 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121090764</v>
+        <v>121093800</v>
       </c>
       <c r="B49" t="n">
-        <v>94484</v>
+        <v>57367</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695871</v>
+        <v>696239</v>
       </c>
       <c r="R49" t="n">
-        <v>6603412</v>
+        <v>6603325</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6142,7 +6181,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6152,12 +6191,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6184,10 +6218,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121091126</v>
+        <v>121092954</v>
       </c>
       <c r="B50" t="n">
-        <v>78601</v>
+        <v>94747</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6196,41 +6230,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696034</v>
+        <v>696174</v>
       </c>
       <c r="R50" t="n">
-        <v>6603209</v>
+        <v>6603210</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6259,7 +6293,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6269,7 +6303,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6296,7 +6330,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121094501</v>
+        <v>121094438</v>
       </c>
       <c r="B51" t="n">
         <v>5169</v>
@@ -6341,10 +6375,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696380</v>
+        <v>696484</v>
       </c>
       <c r="R51" t="n">
-        <v>6603325</v>
+        <v>6603311</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6376,7 +6410,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6386,7 +6420,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6413,10 +6447,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121099960</v>
+        <v>121090597</v>
       </c>
       <c r="B52" t="n">
-        <v>91156</v>
+        <v>94700</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6425,25 +6459,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5467</v>
+        <v>210</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6453,13 +6487,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695863</v>
+        <v>695897</v>
       </c>
       <c r="R52" t="n">
-        <v>6603398</v>
+        <v>6603417</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6483,27 +6517,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6514,26 +6543,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6550,10 +6559,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121095299</v>
+        <v>121095265</v>
       </c>
       <c r="B53" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6562,43 +6571,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696094</v>
+        <v>696112</v>
       </c>
       <c r="R53" t="n">
-        <v>6603186</v>
+        <v>6603209</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6667,37 +6671,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121091319</v>
+        <v>121090764</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6707,13 +6711,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696097</v>
+        <v>695871</v>
       </c>
       <c r="R54" t="n">
-        <v>6603185</v>
+        <v>6603412</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6742,7 +6746,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6752,7 +6756,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6779,10 +6788,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121093973</v>
+        <v>121090910</v>
       </c>
       <c r="B55" t="n">
-        <v>91985</v>
+        <v>100347</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,34 +6804,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696429</v>
+        <v>695893</v>
       </c>
       <c r="R55" t="n">
-        <v>6603315</v>
+        <v>6603281</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6890,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121093800</v>
+        <v>121093973</v>
       </c>
       <c r="B56" t="n">
-        <v>57367</v>
+        <v>91985</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6893,46 +6902,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696239</v>
+        <v>696429</v>
       </c>
       <c r="R56" t="n">
-        <v>6603325</v>
+        <v>6603315</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6959,19 +6963,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6986,22 +6980,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121092954</v>
+        <v>121094501</v>
       </c>
       <c r="B57" t="n">
-        <v>94747</v>
+        <v>5169</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7014,37 +7008,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696174</v>
+        <v>696380</v>
       </c>
       <c r="R57" t="n">
-        <v>6603210</v>
+        <v>6603325</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7073,7 +7072,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7083,7 +7082,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7110,10 +7109,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121091204</v>
+        <v>121090442</v>
       </c>
       <c r="B58" t="n">
-        <v>100347</v>
+        <v>79586</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7126,34 +7125,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696104</v>
+        <v>695921</v>
       </c>
       <c r="R58" t="n">
-        <v>6603207</v>
+        <v>6603409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7212,10 +7211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121090597</v>
+        <v>121095125</v>
       </c>
       <c r="B59" t="n">
-        <v>94700</v>
+        <v>100347</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7228,37 +7227,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695897</v>
+        <v>696122</v>
       </c>
       <c r="R59" t="n">
-        <v>6603417</v>
+        <v>6603202</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7285,19 +7284,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7312,22 +7301,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121091050</v>
+        <v>121090637</v>
       </c>
       <c r="B60" t="n">
-        <v>8421</v>
+        <v>100347</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7340,43 +7329,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695927</v>
+        <v>695859</v>
       </c>
       <c r="R60" t="n">
-        <v>6603231</v>
+        <v>6603407</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7417,7 +7397,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7436,10 +7415,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121093815</v>
+        <v>121093980</v>
       </c>
       <c r="B61" t="n">
-        <v>5189</v>
+        <v>100347</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7452,42 +7431,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696247</v>
+        <v>696434</v>
       </c>
       <c r="R61" t="n">
-        <v>6603313</v>
+        <v>6603315</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7514,19 +7488,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7541,22 +7505,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121095510</v>
+        <v>121090488</v>
       </c>
       <c r="B62" t="n">
-        <v>5189</v>
+        <v>79586</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7569,39 +7533,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696021</v>
+        <v>695888</v>
       </c>
       <c r="R62" t="n">
-        <v>6603152</v>
+        <v>6603408</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7633,7 +7592,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7643,7 +7602,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7654,6 +7613,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7670,10 +7649,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121094438</v>
+        <v>121099960</v>
       </c>
       <c r="B63" t="n">
-        <v>5169</v>
+        <v>91156</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7682,46 +7661,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>5467</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696484</v>
+        <v>695863</v>
       </c>
       <c r="R63" t="n">
-        <v>6603311</v>
+        <v>6603398</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7745,22 +7719,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7771,6 +7750,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7787,7 +7786,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121095125</v>
+        <v>121091204</v>
       </c>
       <c r="B64" t="n">
         <v>100347</v>
@@ -7827,10 +7826,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696122</v>
+        <v>696104</v>
       </c>
       <c r="R64" t="n">
-        <v>6603202</v>
+        <v>6603207</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7889,10 +7888,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121090573</v>
+        <v>121091050</v>
       </c>
       <c r="B65" t="n">
-        <v>94700</v>
+        <v>8421</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7905,43 +7904,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695901</v>
+        <v>695927</v>
       </c>
       <c r="R65" t="n">
-        <v>6603407</v>
+        <v>6603231</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7982,6 +7981,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8000,10 +8000,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121093817</v>
+        <v>121093815</v>
       </c>
       <c r="B66" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8016,21 +8016,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696239</v>
+        <v>696247</v>
       </c>
       <c r="R66" t="n">
-        <v>6603315</v>
+        <v>6603313</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121404815</v>
+        <v>121402734</v>
       </c>
       <c r="B68" t="n">
-        <v>94484</v>
+        <v>57367</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8231,38 +8231,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695864</v>
+        <v>696145</v>
       </c>
       <c r="R68" t="n">
-        <v>6603266</v>
+        <v>6603212</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8292,9 +8297,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8309,19 +8324,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121402388</v>
+        <v>121404558</v>
       </c>
       <c r="B69" t="n">
         <v>57367</v>
@@ -8357,19 +8372,19 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695971</v>
+        <v>695865</v>
       </c>
       <c r="R69" t="n">
-        <v>6603090</v>
+        <v>6603318</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8399,9 +8414,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8416,22 +8441,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121404558</v>
+        <v>121402404</v>
       </c>
       <c r="B70" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8440,43 +8465,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695865</v>
+        <v>695942</v>
       </c>
       <c r="R70" t="n">
-        <v>6603318</v>
+        <v>6603075</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8506,19 +8531,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8533,22 +8548,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121402709</v>
+        <v>121402355</v>
       </c>
       <c r="B71" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8557,20 +8572,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8581,19 +8596,19 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696025</v>
+        <v>696001</v>
       </c>
       <c r="R71" t="n">
-        <v>6603166</v>
+        <v>6603109</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8652,10 +8667,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121405386</v>
+        <v>121402388</v>
       </c>
       <c r="B72" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8664,38 +8679,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696099</v>
+        <v>695971</v>
       </c>
       <c r="R72" t="n">
-        <v>6603163</v>
+        <v>6603090</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8754,10 +8774,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121402355</v>
+        <v>121402709</v>
       </c>
       <c r="B73" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8766,20 +8786,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8790,19 +8810,19 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696001</v>
+        <v>696025</v>
       </c>
       <c r="R73" t="n">
-        <v>6603109</v>
+        <v>6603166</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8861,10 +8881,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121404366</v>
+        <v>121405694</v>
       </c>
       <c r="B74" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8873,38 +8893,52 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695857</v>
+        <v>695999</v>
       </c>
       <c r="R74" t="n">
-        <v>6603366</v>
+        <v>6603117</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8934,9 +8968,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8951,22 +9000,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121404209</v>
+        <v>121402352</v>
       </c>
       <c r="B75" t="n">
-        <v>94484</v>
+        <v>57367</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8975,38 +9024,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695935</v>
+        <v>696013</v>
       </c>
       <c r="R75" t="n">
-        <v>6603415</v>
+        <v>6603120</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9065,7 +9119,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404249</v>
+        <v>121402402</v>
       </c>
       <c r="B76" t="n">
         <v>57367</v>
@@ -9101,19 +9155,19 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695896</v>
+        <v>695942</v>
       </c>
       <c r="R76" t="n">
-        <v>6603382</v>
+        <v>6603075</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9172,10 +9226,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121402809</v>
+        <v>121403961</v>
       </c>
       <c r="B77" t="n">
-        <v>57367</v>
+        <v>79682</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9188,39 +9242,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696135</v>
+        <v>695886</v>
       </c>
       <c r="R77" t="n">
-        <v>6603162</v>
+        <v>6603243</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9250,9 +9299,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9267,22 +9331,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402352</v>
+        <v>121404898</v>
       </c>
       <c r="B78" t="n">
-        <v>57367</v>
+        <v>8421</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9291,31 +9355,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9324,10 +9388,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696013</v>
+        <v>696024</v>
       </c>
       <c r="R78" t="n">
-        <v>6603120</v>
+        <v>6603210</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9386,10 +9450,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404293</v>
+        <v>121404569</v>
       </c>
       <c r="B79" t="n">
-        <v>5169</v>
+        <v>4772</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9402,21 +9466,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9431,10 +9495,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695856</v>
+        <v>695858</v>
       </c>
       <c r="R79" t="n">
-        <v>6603367</v>
+        <v>6603299</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9493,10 +9557,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402404</v>
+        <v>121405386</v>
       </c>
       <c r="B80" t="n">
-        <v>5169</v>
+        <v>90662</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9509,39 +9573,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695942</v>
+        <v>696099</v>
       </c>
       <c r="R80" t="n">
-        <v>6603075</v>
+        <v>6603163</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9600,10 +9659,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404898</v>
+        <v>121404366</v>
       </c>
       <c r="B81" t="n">
-        <v>8421</v>
+        <v>90697</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9612,43 +9671,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696024</v>
+        <v>695857</v>
       </c>
       <c r="R81" t="n">
-        <v>6603210</v>
+        <v>6603366</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9707,10 +9761,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404539</v>
+        <v>121404545</v>
       </c>
       <c r="B82" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9719,43 +9773,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695869</v>
+        <v>695870</v>
       </c>
       <c r="R82" t="n">
-        <v>6603281</v>
+        <v>6603295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9814,10 +9863,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404569</v>
+        <v>121404293</v>
       </c>
       <c r="B83" t="n">
-        <v>4772</v>
+        <v>5169</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9830,21 +9879,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9859,10 +9908,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695858</v>
+        <v>695856</v>
       </c>
       <c r="R83" t="n">
-        <v>6603299</v>
+        <v>6603367</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9921,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121403961</v>
+        <v>121402809</v>
       </c>
       <c r="B84" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9937,34 +9986,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695886</v>
+        <v>696135</v>
       </c>
       <c r="R84" t="n">
-        <v>6603243</v>
+        <v>6603162</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9994,24 +10048,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10026,22 +10065,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121405694</v>
+        <v>121404539</v>
       </c>
       <c r="B85" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10050,52 +10089,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695999</v>
+        <v>695869</v>
       </c>
       <c r="R85" t="n">
-        <v>6603117</v>
+        <v>6603281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10125,24 +10155,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10157,22 +10172,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404545</v>
+        <v>121404249</v>
       </c>
       <c r="B86" t="n">
-        <v>8432</v>
+        <v>57367</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10181,38 +10196,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695870</v>
+        <v>695896</v>
       </c>
       <c r="R86" t="n">
-        <v>6603295</v>
+        <v>6603382</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10271,10 +10291,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121402402</v>
+        <v>121404815</v>
       </c>
       <c r="B87" t="n">
-        <v>57367</v>
+        <v>94484</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10283,43 +10303,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695942</v>
+        <v>695864</v>
       </c>
       <c r="R87" t="n">
-        <v>6603075</v>
+        <v>6603266</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10378,10 +10393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121402734</v>
+        <v>121404209</v>
       </c>
       <c r="B88" t="n">
-        <v>57367</v>
+        <v>94484</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10390,43 +10405,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696145</v>
+        <v>695935</v>
       </c>
       <c r="R88" t="n">
-        <v>6603212</v>
+        <v>6603415</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10456,19 +10466,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10483,12 +10483,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -5526,10 +5526,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121095837</v>
+        <v>121091126</v>
       </c>
       <c r="B44" t="n">
-        <v>5189</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5538,43 +5538,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695989</v>
+        <v>696034</v>
       </c>
       <c r="R44" t="n">
-        <v>6603160</v>
+        <v>6603209</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5606,7 +5601,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5616,7 +5611,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5643,10 +5638,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121091126</v>
+        <v>121095837</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>5189</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5655,38 +5650,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696034</v>
+        <v>695989</v>
       </c>
       <c r="R45" t="n">
-        <v>6603209</v>
+        <v>6603160</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5984,10 +5984,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121095510</v>
+        <v>121093800</v>
       </c>
       <c r="B48" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5996,20 +5996,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6020,22 +6020,22 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696021</v>
+        <v>696239</v>
       </c>
       <c r="R48" t="n">
-        <v>6603152</v>
+        <v>6603325</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6101,10 +6101,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121093800</v>
+        <v>121095510</v>
       </c>
       <c r="B49" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6113,20 +6113,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6137,22 +6137,22 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696239</v>
+        <v>696021</v>
       </c>
       <c r="R49" t="n">
-        <v>6603325</v>
+        <v>6603152</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6671,14 +6671,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121090764</v>
+        <v>121093973</v>
       </c>
       <c r="B54" t="n">
-        <v>94484</v>
+        <v>91985</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6687,37 +6687,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2809</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>695871</v>
+        <v>696429</v>
       </c>
       <c r="R54" t="n">
-        <v>6603412</v>
+        <v>6603315</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6744,24 +6744,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6776,26 +6761,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121090910</v>
+        <v>121090764</v>
       </c>
       <c r="B55" t="n">
-        <v>100347</v>
+        <v>94484</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6804,37 +6789,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>695893</v>
+        <v>695871</v>
       </c>
       <c r="R55" t="n">
-        <v>6603281</v>
+        <v>6603412</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6861,9 +6846,24 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6878,22 +6878,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121093973</v>
+        <v>121094501</v>
       </c>
       <c r="B56" t="n">
-        <v>91985</v>
+        <v>5169</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6906,37 +6906,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696429</v>
+        <v>696380</v>
       </c>
       <c r="R56" t="n">
-        <v>6603315</v>
+        <v>6603325</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6963,9 +6968,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6980,22 +6995,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121094501</v>
+        <v>121090910</v>
       </c>
       <c r="B57" t="n">
-        <v>5169</v>
+        <v>100347</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7008,42 +7023,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696380</v>
+        <v>695893</v>
       </c>
       <c r="R57" t="n">
-        <v>6603325</v>
+        <v>6603281</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7070,19 +7080,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7097,22 +7097,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121090442</v>
+        <v>121095125</v>
       </c>
       <c r="B58" t="n">
-        <v>79586</v>
+        <v>100347</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7125,34 +7125,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>695921</v>
+        <v>696122</v>
       </c>
       <c r="R58" t="n">
-        <v>6603409</v>
+        <v>6603202</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7211,10 +7211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121095125</v>
+        <v>121090442</v>
       </c>
       <c r="B59" t="n">
-        <v>100347</v>
+        <v>79586</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7227,34 +7227,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696122</v>
+        <v>695921</v>
       </c>
       <c r="R59" t="n">
-        <v>6603202</v>
+        <v>6603409</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -9761,10 +9761,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404545</v>
+        <v>121404293</v>
       </c>
       <c r="B82" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9777,34 +9777,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695870</v>
+        <v>695856</v>
       </c>
       <c r="R82" t="n">
-        <v>6603295</v>
+        <v>6603367</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9863,10 +9868,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404293</v>
+        <v>121404545</v>
       </c>
       <c r="B83" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9879,39 +9884,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695856</v>
+        <v>695870</v>
       </c>
       <c r="R83" t="n">
-        <v>6603367</v>
+        <v>6603295</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -4865,10 +4865,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121090573</v>
+        <v>121090488</v>
       </c>
       <c r="B38" t="n">
-        <v>94700</v>
+        <v>79589</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4881,46 +4881,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695901</v>
+        <v>695888</v>
       </c>
       <c r="R38" t="n">
-        <v>6603407</v>
+        <v>6603408</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4947,11 +4938,21 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4960,26 +4961,46 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121091232</v>
+        <v>121091050</v>
       </c>
       <c r="B39" t="n">
-        <v>90697</v>
+        <v>8421</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4988,38 +5009,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696101</v>
+        <v>695927</v>
       </c>
       <c r="R39" t="n">
-        <v>6603200</v>
+        <v>6603231</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5060,6 +5090,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5078,10 +5109,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121091186</v>
+        <v>121093817</v>
       </c>
       <c r="B40" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5090,38 +5121,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696070</v>
+        <v>696239</v>
       </c>
       <c r="R40" t="n">
-        <v>6603197</v>
+        <v>6603315</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5153,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5163,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5190,10 +5226,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121090372</v>
+        <v>121094501</v>
       </c>
       <c r="B41" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5202,38 +5238,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695883</v>
+        <v>696380</v>
       </c>
       <c r="R41" t="n">
-        <v>6603408</v>
+        <v>6603325</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5265,7 +5306,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5275,7 +5316,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5302,10 +5343,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121095556</v>
+        <v>121090442</v>
       </c>
       <c r="B42" t="n">
-        <v>57367</v>
+        <v>79589</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5314,43 +5355,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695980</v>
+        <v>695921</v>
       </c>
       <c r="R42" t="n">
-        <v>6603096</v>
+        <v>6603409</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5409,10 +5445,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121093817</v>
+        <v>121090597</v>
       </c>
       <c r="B43" t="n">
-        <v>5169</v>
+        <v>94712</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5425,39 +5461,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696239</v>
+        <v>695897</v>
       </c>
       <c r="R43" t="n">
-        <v>6603315</v>
+        <v>6603417</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5489,7 +5520,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5499,7 +5530,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5526,10 +5557,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121091126</v>
+        <v>121092954</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>94759</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5538,41 +5569,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696034</v>
+        <v>696174</v>
       </c>
       <c r="R44" t="n">
-        <v>6603209</v>
+        <v>6603210</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5601,7 +5632,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5611,7 +5642,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5638,10 +5669,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121095837</v>
+        <v>121090910</v>
       </c>
       <c r="B45" t="n">
-        <v>5189</v>
+        <v>100360</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5654,42 +5685,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695989</v>
+        <v>695893</v>
       </c>
       <c r="R45" t="n">
-        <v>6603160</v>
+        <v>6603281</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5716,19 +5742,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5743,22 +5759,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121091319</v>
+        <v>121095299</v>
       </c>
       <c r="B46" t="n">
-        <v>78601</v>
+        <v>5169</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5767,38 +5783,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696097</v>
+        <v>696094</v>
       </c>
       <c r="R46" t="n">
-        <v>6603185</v>
+        <v>6603186</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5830,7 +5851,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5840,7 +5861,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5867,10 +5888,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121095299</v>
+        <v>121090372</v>
       </c>
       <c r="B47" t="n">
-        <v>5169</v>
+        <v>90709</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5879,43 +5900,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696094</v>
+        <v>695883</v>
       </c>
       <c r="R47" t="n">
-        <v>6603186</v>
+        <v>6603408</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5947,7 +5963,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5957,7 +5973,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5984,10 +6000,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121093800</v>
+        <v>121094438</v>
       </c>
       <c r="B48" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5996,31 +6012,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6029,13 +6045,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696239</v>
+        <v>696484</v>
       </c>
       <c r="R48" t="n">
-        <v>6603325</v>
+        <v>6603311</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6064,7 +6080,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6074,7 +6090,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6101,7 +6117,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121095510</v>
+        <v>121093815</v>
       </c>
       <c r="B49" t="n">
         <v>5189</v>
@@ -6142,14 +6158,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696021</v>
+        <v>696247</v>
       </c>
       <c r="R49" t="n">
-        <v>6603152</v>
+        <v>6603313</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6181,7 +6197,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6191,7 +6207,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6218,10 +6234,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121092954</v>
+        <v>121091204</v>
       </c>
       <c r="B50" t="n">
-        <v>94747</v>
+        <v>100360</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6234,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2170</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6258,13 +6274,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696174</v>
+        <v>696104</v>
       </c>
       <c r="R50" t="n">
-        <v>6603210</v>
+        <v>6603207</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6291,19 +6307,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6318,22 +6324,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121094438</v>
+        <v>121095556</v>
       </c>
       <c r="B51" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6342,31 +6348,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6375,13 +6381,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696484</v>
+        <v>695980</v>
       </c>
       <c r="R51" t="n">
-        <v>6603311</v>
+        <v>6603096</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6408,19 +6414,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6435,22 +6431,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121090597</v>
+        <v>121093800</v>
       </c>
       <c r="B52" t="n">
-        <v>94700</v>
+        <v>57367</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6459,41 +6455,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695897</v>
+        <v>696239</v>
       </c>
       <c r="R52" t="n">
-        <v>6603417</v>
+        <v>6603325</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6522,7 +6523,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6532,7 +6533,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6559,10 +6560,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121095265</v>
+        <v>121093980</v>
       </c>
       <c r="B53" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6571,41 +6572,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696112</v>
+        <v>696434</v>
       </c>
       <c r="R53" t="n">
-        <v>6603209</v>
+        <v>6603315</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6632,19 +6633,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6659,22 +6650,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121093973</v>
+        <v>121095265</v>
       </c>
       <c r="B54" t="n">
-        <v>91985</v>
+        <v>90709</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6683,41 +6674,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696429</v>
+        <v>696112</v>
       </c>
       <c r="R54" t="n">
-        <v>6603315</v>
+        <v>6603209</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6744,9 +6735,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6761,26 +6762,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121090764</v>
+        <v>121095837</v>
       </c>
       <c r="B55" t="n">
-        <v>94484</v>
+        <v>5189</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6789,37 +6790,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2809</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>695871</v>
+        <v>695989</v>
       </c>
       <c r="R55" t="n">
-        <v>6603412</v>
+        <v>6603160</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6848,7 +6854,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6858,12 +6864,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6890,10 +6891,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121094501</v>
+        <v>121090637</v>
       </c>
       <c r="B56" t="n">
-        <v>5169</v>
+        <v>100360</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6906,42 +6907,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696380</v>
+        <v>695859</v>
       </c>
       <c r="R56" t="n">
-        <v>6603325</v>
+        <v>6603407</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6968,19 +6964,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6995,22 +6981,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121090910</v>
+        <v>121091232</v>
       </c>
       <c r="B57" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7019,38 +7005,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>695893</v>
+        <v>696101</v>
       </c>
       <c r="R57" t="n">
-        <v>6603281</v>
+        <v>6603200</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7112,7 +7098,7 @@
         <v>121095125</v>
       </c>
       <c r="B58" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7211,10 +7197,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121090442</v>
+        <v>121093973</v>
       </c>
       <c r="B59" t="n">
-        <v>79586</v>
+        <v>91997</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7227,34 +7213,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695921</v>
+        <v>696429</v>
       </c>
       <c r="R59" t="n">
-        <v>6603409</v>
+        <v>6603315</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7313,14 +7299,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121090637</v>
+        <v>121090764</v>
       </c>
       <c r="B60" t="n">
-        <v>100347</v>
+        <v>94496</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7329,37 +7315,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695859</v>
+        <v>695871</v>
       </c>
       <c r="R60" t="n">
-        <v>6603407</v>
+        <v>6603412</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7386,9 +7372,24 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7403,22 +7404,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121093980</v>
+        <v>121095510</v>
       </c>
       <c r="B61" t="n">
-        <v>100347</v>
+        <v>5189</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7431,37 +7432,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696434</v>
+        <v>696021</v>
       </c>
       <c r="R61" t="n">
-        <v>6603315</v>
+        <v>6603152</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7488,9 +7494,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7505,22 +7521,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121090488</v>
+        <v>121091126</v>
       </c>
       <c r="B62" t="n">
-        <v>79586</v>
+        <v>78604</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7529,25 +7545,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7557,10 +7573,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>695888</v>
+        <v>696034</v>
       </c>
       <c r="R62" t="n">
-        <v>6603408</v>
+        <v>6603209</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7592,7 +7608,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7602,7 +7618,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7613,26 +7629,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7649,10 +7645,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121099960</v>
+        <v>121091186</v>
       </c>
       <c r="B63" t="n">
-        <v>91156</v>
+        <v>90709</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7665,21 +7661,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5467</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7689,13 +7685,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>695863</v>
+        <v>696070</v>
       </c>
       <c r="R63" t="n">
-        <v>6603398</v>
+        <v>6603197</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7719,27 +7715,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7750,26 +7741,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7786,10 +7757,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121091204</v>
+        <v>121099960</v>
       </c>
       <c r="B64" t="n">
-        <v>100347</v>
+        <v>91168</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7798,38 +7769,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>5467</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696104</v>
+        <v>695863</v>
       </c>
       <c r="R64" t="n">
-        <v>6603207</v>
+        <v>6603398</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7856,12 +7827,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7872,26 +7858,46 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121091050</v>
+        <v>121091319</v>
       </c>
       <c r="B65" t="n">
-        <v>8421</v>
+        <v>78604</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7900,50 +7906,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695927</v>
+        <v>696097</v>
       </c>
       <c r="R65" t="n">
-        <v>6603231</v>
+        <v>6603185</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7970,40 +7967,49 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121093815</v>
+        <v>121090573</v>
       </c>
       <c r="B66" t="n">
-        <v>5189</v>
+        <v>94712</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8016,42 +8022,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696247</v>
+        <v>695901</v>
       </c>
       <c r="R66" t="n">
-        <v>6603313</v>
+        <v>6603407</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8078,19 +8088,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8105,12 +8105,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8120,7 +8120,7 @@
         <v>121090765</v>
       </c>
       <c r="B67" t="n">
-        <v>94484</v>
+        <v>94496</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121402734</v>
+        <v>121404539</v>
       </c>
       <c r="B68" t="n">
         <v>57367</v>
@@ -8255,19 +8255,19 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696145</v>
+        <v>695869</v>
       </c>
       <c r="R68" t="n">
-        <v>6603212</v>
+        <v>6603281</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8297,19 +8297,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8324,19 +8314,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121404558</v>
+        <v>121402709</v>
       </c>
       <c r="B69" t="n">
         <v>57367</v>
@@ -8372,19 +8362,19 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695865</v>
+        <v>696025</v>
       </c>
       <c r="R69" t="n">
-        <v>6603318</v>
+        <v>6603166</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8414,19 +8404,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8441,22 +8421,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121402404</v>
+        <v>121402352</v>
       </c>
       <c r="B70" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8465,31 +8445,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8498,10 +8478,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695942</v>
+        <v>696013</v>
       </c>
       <c r="R70" t="n">
-        <v>6603075</v>
+        <v>6603120</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8560,10 +8540,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121402355</v>
+        <v>121404293</v>
       </c>
       <c r="B71" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8576,21 +8556,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8605,10 +8585,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696001</v>
+        <v>695856</v>
       </c>
       <c r="R71" t="n">
-        <v>6603109</v>
+        <v>6603367</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8667,7 +8647,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121402388</v>
+        <v>121402734</v>
       </c>
       <c r="B72" t="n">
         <v>57367</v>
@@ -8703,19 +8683,19 @@
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695971</v>
+        <v>696145</v>
       </c>
       <c r="R72" t="n">
-        <v>6603090</v>
+        <v>6603212</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8745,9 +8725,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8762,22 +8752,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121402709</v>
+        <v>121404815</v>
       </c>
       <c r="B73" t="n">
-        <v>57367</v>
+        <v>94496</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8786,43 +8776,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696025</v>
+        <v>695864</v>
       </c>
       <c r="R73" t="n">
-        <v>6603166</v>
+        <v>6603266</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8881,10 +8866,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121405694</v>
+        <v>121404249</v>
       </c>
       <c r="B74" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8893,52 +8878,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695999</v>
+        <v>695896</v>
       </c>
       <c r="R74" t="n">
-        <v>6603117</v>
+        <v>6603382</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8968,24 +8944,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9000,22 +8961,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121402352</v>
+        <v>121404569</v>
       </c>
       <c r="B75" t="n">
-        <v>57367</v>
+        <v>4772</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9024,43 +8985,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696013</v>
+        <v>695858</v>
       </c>
       <c r="R75" t="n">
-        <v>6603120</v>
+        <v>6603299</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9119,7 +9080,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402402</v>
+        <v>121402388</v>
       </c>
       <c r="B76" t="n">
         <v>57367</v>
@@ -9160,14 +9121,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695942</v>
+        <v>695971</v>
       </c>
       <c r="R76" t="n">
-        <v>6603075</v>
+        <v>6603090</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9226,10 +9187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121403961</v>
+        <v>121404558</v>
       </c>
       <c r="B77" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9242,34 +9203,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695886</v>
+        <v>695865</v>
       </c>
       <c r="R77" t="n">
-        <v>6603243</v>
+        <v>6603318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9301,7 +9267,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9311,12 +9277,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9336,17 +9297,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404898</v>
+        <v>121402402</v>
       </c>
       <c r="B78" t="n">
-        <v>8421</v>
+        <v>57367</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9355,31 +9316,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9388,10 +9349,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696024</v>
+        <v>695942</v>
       </c>
       <c r="R78" t="n">
-        <v>6603210</v>
+        <v>6603075</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9450,10 +9411,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404569</v>
+        <v>121405386</v>
       </c>
       <c r="B79" t="n">
-        <v>4772</v>
+        <v>90674</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9466,39 +9427,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695858</v>
+        <v>696099</v>
       </c>
       <c r="R79" t="n">
-        <v>6603299</v>
+        <v>6603163</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9557,10 +9513,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121405386</v>
+        <v>121404209</v>
       </c>
       <c r="B80" t="n">
-        <v>90662</v>
+        <v>94496</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9573,21 +9529,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9597,10 +9553,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696099</v>
+        <v>695935</v>
       </c>
       <c r="R80" t="n">
-        <v>6603163</v>
+        <v>6603415</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9662,7 +9618,7 @@
         <v>121404366</v>
       </c>
       <c r="B81" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9761,7 +9717,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404293</v>
+        <v>121402404</v>
       </c>
       <c r="B82" t="n">
         <v>5169</v>
@@ -9802,14 +9758,14 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695856</v>
+        <v>695942</v>
       </c>
       <c r="R82" t="n">
-        <v>6603367</v>
+        <v>6603075</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9868,10 +9824,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404545</v>
+        <v>121402355</v>
       </c>
       <c r="B83" t="n">
-        <v>8432</v>
+        <v>5189</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9884,34 +9840,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695870</v>
+        <v>696001</v>
       </c>
       <c r="R83" t="n">
-        <v>6603295</v>
+        <v>6603109</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10077,10 +10038,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404539</v>
+        <v>121404545</v>
       </c>
       <c r="B85" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10089,43 +10050,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695869</v>
+        <v>695870</v>
       </c>
       <c r="R85" t="n">
-        <v>6603281</v>
+        <v>6603295</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10184,10 +10140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404249</v>
+        <v>121405694</v>
       </c>
       <c r="B86" t="n">
-        <v>57367</v>
+        <v>98094</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10196,43 +10152,52 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695896</v>
+        <v>695999</v>
       </c>
       <c r="R86" t="n">
-        <v>6603382</v>
+        <v>6603117</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10262,9 +10227,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10279,22 +10259,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404815</v>
+        <v>121403961</v>
       </c>
       <c r="B87" t="n">
-        <v>94484</v>
+        <v>79685</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10303,38 +10283,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695864</v>
+        <v>695886</v>
       </c>
       <c r="R87" t="n">
-        <v>6603266</v>
+        <v>6603243</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10364,9 +10344,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10381,22 +10376,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404209</v>
+        <v>121404898</v>
       </c>
       <c r="B88" t="n">
-        <v>94484</v>
+        <v>8421</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10409,34 +10404,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2809</v>
+        <v>106554</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695935</v>
+        <v>696024</v>
       </c>
       <c r="R88" t="n">
-        <v>6603415</v>
+        <v>6603210</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -4865,10 +4865,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121090488</v>
+        <v>121095125</v>
       </c>
       <c r="B38" t="n">
-        <v>79589</v>
+        <v>100361</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4881,37 +4881,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695888</v>
+        <v>696122</v>
       </c>
       <c r="R38" t="n">
-        <v>6603408</v>
+        <v>6603202</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4938,21 +4938,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4961,46 +4951,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121091050</v>
+        <v>121095265</v>
       </c>
       <c r="B39" t="n">
-        <v>8421</v>
+        <v>90710</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5009,50 +4979,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695927</v>
+        <v>696112</v>
       </c>
       <c r="R39" t="n">
-        <v>6603231</v>
+        <v>6603209</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,37 +5040,46 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121093817</v>
+        <v>121095299</v>
       </c>
       <c r="B40" t="n">
         <v>5169</v>
@@ -5150,14 +5120,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696239</v>
+        <v>696094</v>
       </c>
       <c r="R40" t="n">
-        <v>6603315</v>
+        <v>6603186</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5189,7 +5159,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5169,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5226,10 +5196,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121094501</v>
+        <v>121091186</v>
       </c>
       <c r="B41" t="n">
-        <v>5169</v>
+        <v>90710</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5238,43 +5208,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696380</v>
+        <v>696070</v>
       </c>
       <c r="R41" t="n">
-        <v>6603325</v>
+        <v>6603197</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5306,7 +5271,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5316,7 +5281,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5343,10 +5308,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121090442</v>
+        <v>121092954</v>
       </c>
       <c r="B42" t="n">
-        <v>79589</v>
+        <v>94760</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5359,37 +5324,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>2170</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695921</v>
+        <v>696174</v>
       </c>
       <c r="R42" t="n">
-        <v>6603409</v>
+        <v>6603210</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5416,9 +5381,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,22 +5408,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121090597</v>
+        <v>121090637</v>
       </c>
       <c r="B43" t="n">
-        <v>94712</v>
+        <v>100361</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5461,37 +5436,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695897</v>
+        <v>695859</v>
       </c>
       <c r="R43" t="n">
-        <v>6603417</v>
+        <v>6603407</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5518,19 +5493,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5545,22 +5510,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121092954</v>
+        <v>121094501</v>
       </c>
       <c r="B44" t="n">
-        <v>94759</v>
+        <v>5169</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5573,37 +5538,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696174</v>
+        <v>696380</v>
       </c>
       <c r="R44" t="n">
-        <v>6603210</v>
+        <v>6603325</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5632,7 +5602,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5642,7 +5612,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5669,10 +5639,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121090910</v>
+        <v>121090597</v>
       </c>
       <c r="B45" t="n">
-        <v>100360</v>
+        <v>94713</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5685,37 +5655,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695893</v>
+        <v>695897</v>
       </c>
       <c r="R45" t="n">
-        <v>6603281</v>
+        <v>6603417</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,9 +5712,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5759,22 +5739,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121095299</v>
+        <v>121093800</v>
       </c>
       <c r="B46" t="n">
-        <v>5169</v>
+        <v>57367</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5783,46 +5763,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696094</v>
+        <v>696239</v>
       </c>
       <c r="R46" t="n">
-        <v>6603186</v>
+        <v>6603325</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5851,7 +5831,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5861,7 +5841,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5888,10 +5868,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121090372</v>
+        <v>121095837</v>
       </c>
       <c r="B47" t="n">
-        <v>90709</v>
+        <v>5189</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5900,38 +5880,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695883</v>
+        <v>695989</v>
       </c>
       <c r="R47" t="n">
-        <v>6603408</v>
+        <v>6603160</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5963,7 +5948,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5973,7 +5958,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6000,10 +5985,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121094438</v>
+        <v>121091126</v>
       </c>
       <c r="B48" t="n">
-        <v>5169</v>
+        <v>78604</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6012,43 +5997,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696484</v>
+        <v>696034</v>
       </c>
       <c r="R48" t="n">
-        <v>6603311</v>
+        <v>6603209</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6080,7 +6060,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6090,7 +6070,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6117,10 +6097,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121093815</v>
+        <v>121099960</v>
       </c>
       <c r="B49" t="n">
-        <v>5189</v>
+        <v>91169</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6129,46 +6109,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>5467</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696247</v>
+        <v>695863</v>
       </c>
       <c r="R49" t="n">
-        <v>6603313</v>
+        <v>6603398</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6192,22 +6167,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6218,6 +6198,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121091204</v>
+        <v>121093973</v>
       </c>
       <c r="B50" t="n">
-        <v>100360</v>
+        <v>91998</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696104</v>
+        <v>696429</v>
       </c>
       <c r="R50" t="n">
-        <v>6603207</v>
+        <v>6603315</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121095556</v>
+        <v>121093980</v>
       </c>
       <c r="B51" t="n">
-        <v>57367</v>
+        <v>100361</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6348,43 +6348,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695980</v>
+        <v>696434</v>
       </c>
       <c r="R51" t="n">
-        <v>6603096</v>
+        <v>6603315</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6443,10 +6438,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121093800</v>
+        <v>121093815</v>
       </c>
       <c r="B52" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6455,20 +6450,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6479,7 +6474,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6488,13 +6483,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696239</v>
+        <v>696247</v>
       </c>
       <c r="R52" t="n">
-        <v>6603325</v>
+        <v>6603313</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6523,7 +6518,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6533,7 +6528,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6560,10 +6555,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121093980</v>
+        <v>121091050</v>
       </c>
       <c r="B53" t="n">
-        <v>100360</v>
+        <v>8421</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6576,34 +6571,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696434</v>
+        <v>695927</v>
       </c>
       <c r="R53" t="n">
-        <v>6603315</v>
+        <v>6603231</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6644,6 +6648,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6662,10 +6667,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121095265</v>
+        <v>121090372</v>
       </c>
       <c r="B54" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6702,10 +6707,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696112</v>
+        <v>695883</v>
       </c>
       <c r="R54" t="n">
-        <v>6603209</v>
+        <v>6603408</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6737,7 +6742,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6747,7 +6752,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6774,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121095837</v>
+        <v>121090442</v>
       </c>
       <c r="B55" t="n">
-        <v>5189</v>
+        <v>79589</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6790,42 +6795,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>695989</v>
+        <v>695921</v>
       </c>
       <c r="R55" t="n">
-        <v>6603160</v>
+        <v>6603409</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6852,19 +6852,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6879,22 +6869,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121090637</v>
+        <v>121090488</v>
       </c>
       <c r="B56" t="n">
-        <v>100360</v>
+        <v>79589</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6907,37 +6897,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>695859</v>
+        <v>695888</v>
       </c>
       <c r="R56" t="n">
-        <v>6603407</v>
+        <v>6603408</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6964,11 +6954,21 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6977,26 +6977,46 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121091232</v>
+        <v>121094438</v>
       </c>
       <c r="B57" t="n">
-        <v>90709</v>
+        <v>5169</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7005,41 +7025,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696101</v>
+        <v>696484</v>
       </c>
       <c r="R57" t="n">
-        <v>6603200</v>
+        <v>6603311</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7066,9 +7091,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7083,22 +7118,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121095125</v>
+        <v>121091204</v>
       </c>
       <c r="B58" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7135,10 +7170,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696122</v>
+        <v>696104</v>
       </c>
       <c r="R58" t="n">
-        <v>6603202</v>
+        <v>6603207</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7197,10 +7232,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121093973</v>
+        <v>121090910</v>
       </c>
       <c r="B59" t="n">
-        <v>91997</v>
+        <v>100361</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7213,34 +7248,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696429</v>
+        <v>695893</v>
       </c>
       <c r="R59" t="n">
-        <v>6603315</v>
+        <v>6603281</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7299,14 +7334,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121090764</v>
+        <v>121090573</v>
       </c>
       <c r="B60" t="n">
-        <v>94496</v>
+        <v>94713</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7315,37 +7350,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695871</v>
+        <v>695901</v>
       </c>
       <c r="R60" t="n">
-        <v>6603412</v>
+        <v>6603407</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7372,24 +7416,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7404,26 +7433,26 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121095510</v>
+        <v>121090764</v>
       </c>
       <c r="B61" t="n">
-        <v>5189</v>
+        <v>94497</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7432,42 +7461,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>2809</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696021</v>
+        <v>695871</v>
       </c>
       <c r="R61" t="n">
-        <v>6603152</v>
+        <v>6603412</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7496,7 +7520,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7506,7 +7530,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7533,10 +7562,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121091126</v>
+        <v>121093817</v>
       </c>
       <c r="B62" t="n">
-        <v>78604</v>
+        <v>5169</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7545,38 +7574,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696034</v>
+        <v>696239</v>
       </c>
       <c r="R62" t="n">
-        <v>6603209</v>
+        <v>6603315</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7608,7 +7642,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7618,7 +7652,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7645,10 +7679,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121091186</v>
+        <v>121091232</v>
       </c>
       <c r="B63" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7681,17 +7715,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696070</v>
+        <v>696101</v>
       </c>
       <c r="R63" t="n">
-        <v>6603197</v>
+        <v>6603200</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7718,19 +7752,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7745,22 +7769,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121099960</v>
+        <v>121091319</v>
       </c>
       <c r="B64" t="n">
-        <v>91168</v>
+        <v>78604</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7773,21 +7797,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7797,13 +7821,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>695863</v>
+        <v>696097</v>
       </c>
       <c r="R64" t="n">
-        <v>6603398</v>
+        <v>6603185</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7827,27 +7851,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7858,26 +7877,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7894,10 +7893,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121091319</v>
+        <v>121095556</v>
       </c>
       <c r="B65" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7910,37 +7909,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696097</v>
+        <v>695980</v>
       </c>
       <c r="R65" t="n">
-        <v>6603185</v>
+        <v>6603096</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7967,19 +7971,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7994,22 +7988,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121090573</v>
+        <v>121095510</v>
       </c>
       <c r="B66" t="n">
-        <v>94712</v>
+        <v>5189</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8022,46 +8016,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>695901</v>
+        <v>696021</v>
       </c>
       <c r="R66" t="n">
-        <v>6603407</v>
+        <v>6603152</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8088,9 +8078,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8105,12 +8105,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8120,7 +8120,7 @@
         <v>121090765</v>
       </c>
       <c r="B67" t="n">
-        <v>94496</v>
+        <v>94497</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121404539</v>
+        <v>121404558</v>
       </c>
       <c r="B68" t="n">
         <v>57367</v>
@@ -8255,19 +8255,19 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695869</v>
+        <v>695865</v>
       </c>
       <c r="R68" t="n">
-        <v>6603281</v>
+        <v>6603318</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8297,9 +8297,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8314,19 +8324,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121402709</v>
+        <v>121402402</v>
       </c>
       <c r="B69" t="n">
         <v>57367</v>
@@ -8362,7 +8372,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8371,10 +8381,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696025</v>
+        <v>695942</v>
       </c>
       <c r="R69" t="n">
-        <v>6603166</v>
+        <v>6603075</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8433,10 +8443,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121402352</v>
+        <v>121404293</v>
       </c>
       <c r="B70" t="n">
-        <v>57367</v>
+        <v>5169</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8445,43 +8455,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696013</v>
+        <v>695856</v>
       </c>
       <c r="R70" t="n">
-        <v>6603120</v>
+        <v>6603367</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8540,10 +8550,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121404293</v>
+        <v>121404545</v>
       </c>
       <c r="B71" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8556,39 +8566,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695856</v>
+        <v>695870</v>
       </c>
       <c r="R71" t="n">
-        <v>6603367</v>
+        <v>6603295</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8647,10 +8652,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121402734</v>
+        <v>121404815</v>
       </c>
       <c r="B72" t="n">
-        <v>57367</v>
+        <v>94497</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8659,43 +8664,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696145</v>
+        <v>695864</v>
       </c>
       <c r="R72" t="n">
-        <v>6603212</v>
+        <v>6603266</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8725,19 +8725,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8752,22 +8742,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121404815</v>
+        <v>121402709</v>
       </c>
       <c r="B73" t="n">
-        <v>94496</v>
+        <v>57367</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8776,38 +8766,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695864</v>
+        <v>696025</v>
       </c>
       <c r="R73" t="n">
-        <v>6603266</v>
+        <v>6603166</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8866,10 +8861,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121404249</v>
+        <v>121402355</v>
       </c>
       <c r="B74" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8878,20 +8873,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8902,7 +8897,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8911,10 +8906,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695896</v>
+        <v>696001</v>
       </c>
       <c r="R74" t="n">
-        <v>6603382</v>
+        <v>6603109</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8973,10 +8968,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121404569</v>
+        <v>121402388</v>
       </c>
       <c r="B75" t="n">
-        <v>4772</v>
+        <v>57367</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8985,31 +8980,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9018,10 +9013,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695858</v>
+        <v>695971</v>
       </c>
       <c r="R75" t="n">
-        <v>6603299</v>
+        <v>6603090</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9080,7 +9075,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402388</v>
+        <v>121402734</v>
       </c>
       <c r="B76" t="n">
         <v>57367</v>
@@ -9116,19 +9111,19 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695971</v>
+        <v>696145</v>
       </c>
       <c r="R76" t="n">
-        <v>6603090</v>
+        <v>6603212</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9158,9 +9153,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9175,22 +9180,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404558</v>
+        <v>121405386</v>
       </c>
       <c r="B77" t="n">
-        <v>57367</v>
+        <v>90675</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9199,43 +9204,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695865</v>
+        <v>696099</v>
       </c>
       <c r="R77" t="n">
-        <v>6603318</v>
+        <v>6603163</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9265,19 +9265,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9292,19 +9282,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402402</v>
+        <v>121402352</v>
       </c>
       <c r="B78" t="n">
         <v>57367</v>
@@ -9340,7 +9330,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9349,10 +9339,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695942</v>
+        <v>696013</v>
       </c>
       <c r="R78" t="n">
-        <v>6603075</v>
+        <v>6603120</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9411,10 +9401,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121405386</v>
+        <v>121402404</v>
       </c>
       <c r="B79" t="n">
-        <v>90674</v>
+        <v>5169</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9427,34 +9417,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696099</v>
+        <v>695942</v>
       </c>
       <c r="R79" t="n">
-        <v>6603163</v>
+        <v>6603075</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9513,10 +9508,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121404209</v>
+        <v>121405694</v>
       </c>
       <c r="B80" t="n">
-        <v>94496</v>
+        <v>98095</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9525,38 +9520,52 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695935</v>
+        <v>695999</v>
       </c>
       <c r="R80" t="n">
-        <v>6603415</v>
+        <v>6603117</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9586,9 +9595,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9603,22 +9627,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404366</v>
+        <v>121403961</v>
       </c>
       <c r="B81" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9631,34 +9655,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695857</v>
+        <v>695886</v>
       </c>
       <c r="R81" t="n">
-        <v>6603366</v>
+        <v>6603243</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9688,9 +9712,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9705,22 +9744,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121402404</v>
+        <v>121404569</v>
       </c>
       <c r="B82" t="n">
-        <v>5169</v>
+        <v>4772</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9733,21 +9772,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9758,14 +9797,14 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695942</v>
+        <v>695858</v>
       </c>
       <c r="R82" t="n">
-        <v>6603075</v>
+        <v>6603299</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9824,10 +9863,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402355</v>
+        <v>121404249</v>
       </c>
       <c r="B83" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9836,20 +9875,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9860,7 +9899,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9869,10 +9908,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696001</v>
+        <v>695896</v>
       </c>
       <c r="R83" t="n">
-        <v>6603109</v>
+        <v>6603382</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9931,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402809</v>
+        <v>121404898</v>
       </c>
       <c r="B84" t="n">
-        <v>57367</v>
+        <v>8421</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9943,31 +9982,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9976,10 +10015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696135</v>
+        <v>696024</v>
       </c>
       <c r="R84" t="n">
-        <v>6603162</v>
+        <v>6603210</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,10 +10077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404545</v>
+        <v>121404209</v>
       </c>
       <c r="B85" t="n">
-        <v>8432</v>
+        <v>94497</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10054,34 +10093,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>2809</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695870</v>
+        <v>695935</v>
       </c>
       <c r="R85" t="n">
-        <v>6603295</v>
+        <v>6603415</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,10 +10179,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121405694</v>
+        <v>121404366</v>
       </c>
       <c r="B86" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10152,52 +10191,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695999</v>
+        <v>695857</v>
       </c>
       <c r="R86" t="n">
-        <v>6603117</v>
+        <v>6603366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10227,24 +10252,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10259,22 +10269,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121403961</v>
+        <v>121402809</v>
       </c>
       <c r="B87" t="n">
-        <v>79685</v>
+        <v>57367</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10287,34 +10297,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695886</v>
+        <v>696135</v>
       </c>
       <c r="R87" t="n">
-        <v>6603243</v>
+        <v>6603162</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10344,24 +10359,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10376,22 +10376,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404898</v>
+        <v>121404539</v>
       </c>
       <c r="B88" t="n">
-        <v>8421</v>
+        <v>57367</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10400,43 +10400,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696024</v>
+        <v>695869</v>
       </c>
       <c r="R88" t="n">
-        <v>6603210</v>
+        <v>6603281</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -4865,10 +4865,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121095125</v>
+        <v>121091186</v>
       </c>
       <c r="B38" t="n">
-        <v>100361</v>
+        <v>90713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4877,41 +4877,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696122</v>
+        <v>696070</v>
       </c>
       <c r="R38" t="n">
-        <v>6603202</v>
+        <v>6603197</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4938,9 +4938,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4955,22 +4965,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121095265</v>
+        <v>121092954</v>
       </c>
       <c r="B39" t="n">
-        <v>90710</v>
+        <v>94763</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4979,41 +4989,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2170</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696112</v>
+        <v>696174</v>
       </c>
       <c r="R39" t="n">
-        <v>6603209</v>
+        <v>6603210</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5042,7 +5052,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5052,7 +5062,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5079,10 +5089,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121095299</v>
+        <v>121093980</v>
       </c>
       <c r="B40" t="n">
-        <v>5169</v>
+        <v>100364</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5095,42 +5105,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696094</v>
+        <v>696434</v>
       </c>
       <c r="R40" t="n">
-        <v>6603186</v>
+        <v>6603315</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,19 +5162,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5184,22 +5179,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121091186</v>
+        <v>121091319</v>
       </c>
       <c r="B41" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5212,21 +5207,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5236,10 +5231,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696070</v>
+        <v>696097</v>
       </c>
       <c r="R41" t="n">
-        <v>6603197</v>
+        <v>6603185</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5271,7 +5266,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5281,7 +5276,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5308,10 +5303,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121092954</v>
+        <v>121095837</v>
       </c>
       <c r="B42" t="n">
-        <v>94760</v>
+        <v>5192</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5324,37 +5319,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2170</v>
+        <v>105930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696174</v>
+        <v>695989</v>
       </c>
       <c r="R42" t="n">
-        <v>6603210</v>
+        <v>6603160</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5420,10 +5420,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121090637</v>
+        <v>121091232</v>
       </c>
       <c r="B43" t="n">
-        <v>100361</v>
+        <v>90713</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5432,38 +5432,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695859</v>
+        <v>696101</v>
       </c>
       <c r="R43" t="n">
-        <v>6603407</v>
+        <v>6603200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5522,10 +5522,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121094501</v>
+        <v>121090910</v>
       </c>
       <c r="B44" t="n">
-        <v>5169</v>
+        <v>100364</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5538,42 +5538,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696380</v>
+        <v>695893</v>
       </c>
       <c r="R44" t="n">
-        <v>6603325</v>
+        <v>6603281</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5600,19 +5595,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5627,22 +5612,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121090597</v>
+        <v>121091204</v>
       </c>
       <c r="B45" t="n">
-        <v>94713</v>
+        <v>100364</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5655,37 +5640,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695897</v>
+        <v>696104</v>
       </c>
       <c r="R45" t="n">
-        <v>6603417</v>
+        <v>6603207</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5712,19 +5697,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5739,22 +5714,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121093800</v>
+        <v>121090597</v>
       </c>
       <c r="B46" t="n">
-        <v>57367</v>
+        <v>94716</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5763,46 +5738,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696239</v>
+        <v>695897</v>
       </c>
       <c r="R46" t="n">
-        <v>6603325</v>
+        <v>6603417</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5831,7 +5801,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5841,7 +5811,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5868,10 +5838,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121095837</v>
+        <v>121099960</v>
       </c>
       <c r="B47" t="n">
-        <v>5189</v>
+        <v>91172</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5880,46 +5850,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>5467</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695989</v>
+        <v>695863</v>
       </c>
       <c r="R47" t="n">
-        <v>6603160</v>
+        <v>6603398</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5943,22 +5908,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Undersidan av en kraftigt rötad låga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5969,6 +5939,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5985,10 +5975,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121091126</v>
+        <v>121090637</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>100364</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5997,41 +5987,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696034</v>
+        <v>695859</v>
       </c>
       <c r="R48" t="n">
-        <v>6603209</v>
+        <v>6603407</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6058,19 +6048,9 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6085,22 +6065,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121099960</v>
+        <v>121090442</v>
       </c>
       <c r="B49" t="n">
-        <v>91169</v>
+        <v>79592</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6109,38 +6089,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5467</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695863</v>
+        <v>695921</v>
       </c>
       <c r="R49" t="n">
-        <v>6603398</v>
+        <v>6603409</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6167,27 +6147,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Undersidan av en kraftigt rötad låga</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,46 +6163,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121093973</v>
+        <v>121093800</v>
       </c>
       <c r="B50" t="n">
-        <v>91998</v>
+        <v>57370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6246,41 +6191,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696429</v>
+        <v>696239</v>
       </c>
       <c r="R50" t="n">
-        <v>6603315</v>
+        <v>6603325</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6307,9 +6257,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6324,26 +6284,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121093980</v>
+        <v>121090764</v>
       </c>
       <c r="B51" t="n">
-        <v>100361</v>
+        <v>94500</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6352,37 +6312,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696434</v>
+        <v>695871</v>
       </c>
       <c r="R51" t="n">
-        <v>6603315</v>
+        <v>6603412</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6409,9 +6369,24 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Finns på en stor yta på ca 50 kvm</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6426,22 +6401,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121093815</v>
+        <v>121091126</v>
       </c>
       <c r="B52" t="n">
-        <v>5189</v>
+        <v>78607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6450,43 +6425,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696247</v>
+        <v>696034</v>
       </c>
       <c r="R52" t="n">
-        <v>6603313</v>
+        <v>6603209</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6518,7 +6488,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6528,7 +6498,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6555,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121091050</v>
+        <v>121093815</v>
       </c>
       <c r="B53" t="n">
-        <v>8421</v>
+        <v>5192</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6571,46 +6541,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695927</v>
+        <v>696247</v>
       </c>
       <c r="R53" t="n">
-        <v>6603231</v>
+        <v>6603313</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6637,40 +6603,49 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121090372</v>
+        <v>121094501</v>
       </c>
       <c r="B54" t="n">
-        <v>90710</v>
+        <v>5172</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6679,38 +6654,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>695883</v>
+        <v>696380</v>
       </c>
       <c r="R54" t="n">
-        <v>6603408</v>
+        <v>6603325</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6742,7 +6722,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6752,7 +6732,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6779,10 +6759,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121090442</v>
+        <v>121094438</v>
       </c>
       <c r="B55" t="n">
-        <v>79589</v>
+        <v>5172</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,37 +6775,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>695921</v>
+        <v>696484</v>
       </c>
       <c r="R55" t="n">
-        <v>6603409</v>
+        <v>6603311</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6852,9 +6837,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6869,22 +6864,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121090488</v>
+        <v>121093817</v>
       </c>
       <c r="B56" t="n">
-        <v>79589</v>
+        <v>5172</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,34 +6892,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>695888</v>
+        <v>696239</v>
       </c>
       <c r="R56" t="n">
-        <v>6603408</v>
+        <v>6603315</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6977,26 +6977,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7013,10 +6993,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121094438</v>
+        <v>121095265</v>
       </c>
       <c r="B57" t="n">
-        <v>5169</v>
+        <v>90713</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7025,43 +7005,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696484</v>
+        <v>696112</v>
       </c>
       <c r="R57" t="n">
-        <v>6603311</v>
+        <v>6603209</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7093,7 +7068,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7103,7 +7078,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7130,10 +7105,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121091204</v>
+        <v>121095125</v>
       </c>
       <c r="B58" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7170,10 +7145,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696104</v>
+        <v>696122</v>
       </c>
       <c r="R58" t="n">
-        <v>6603207</v>
+        <v>6603202</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7232,10 +7207,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121090910</v>
+        <v>121090573</v>
       </c>
       <c r="B59" t="n">
-        <v>100361</v>
+        <v>94716</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7248,34 +7223,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695893</v>
+        <v>695901</v>
       </c>
       <c r="R59" t="n">
-        <v>6603281</v>
+        <v>6603407</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7334,10 +7318,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121090573</v>
+        <v>121095556</v>
       </c>
       <c r="B60" t="n">
-        <v>94713</v>
+        <v>57370</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7346,47 +7330,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>695901</v>
+        <v>695980</v>
       </c>
       <c r="R60" t="n">
-        <v>6603407</v>
+        <v>6603096</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7445,14 +7425,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121090764</v>
+        <v>121091050</v>
       </c>
       <c r="B61" t="n">
-        <v>94497</v>
+        <v>8424</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7461,37 +7441,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2809</v>
+        <v>106554</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda, Naturskog norr om Gallboda, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695871</v>
+        <v>695927</v>
       </c>
       <c r="R61" t="n">
-        <v>6603412</v>
+        <v>6603231</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7518,54 +7507,40 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Finns på en stor yta på ca 50 kvm</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121093817</v>
+        <v>121090372</v>
       </c>
       <c r="B62" t="n">
-        <v>5169</v>
+        <v>90713</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7574,43 +7549,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696239</v>
+        <v>695883</v>
       </c>
       <c r="R62" t="n">
-        <v>6603315</v>
+        <v>6603408</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7642,7 +7612,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7652,7 +7622,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7679,10 +7649,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121091232</v>
+        <v>121095299</v>
       </c>
       <c r="B63" t="n">
-        <v>90710</v>
+        <v>5172</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7691,41 +7661,46 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696101</v>
+        <v>696094</v>
       </c>
       <c r="R63" t="n">
-        <v>6603200</v>
+        <v>6603186</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7752,9 +7727,19 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7769,22 +7754,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121091319</v>
+        <v>121095510</v>
       </c>
       <c r="B64" t="n">
-        <v>78604</v>
+        <v>5192</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7793,38 +7778,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696097</v>
+        <v>696021</v>
       </c>
       <c r="R64" t="n">
-        <v>6603185</v>
+        <v>6603152</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7856,7 +7846,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7866,7 +7856,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7893,10 +7883,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121095556</v>
+        <v>121093973</v>
       </c>
       <c r="B65" t="n">
-        <v>57367</v>
+        <v>92001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7905,43 +7895,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695980</v>
+        <v>696429</v>
       </c>
       <c r="R65" t="n">
-        <v>6603096</v>
+        <v>6603315</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8000,10 +7985,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121095510</v>
+        <v>121090488</v>
       </c>
       <c r="B66" t="n">
-        <v>5189</v>
+        <v>79592</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8016,39 +8001,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696021</v>
+        <v>695888</v>
       </c>
       <c r="R66" t="n">
-        <v>6603152</v>
+        <v>6603408</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8080,7 +8060,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8090,7 +8070,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8101,6 +8081,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Leuciscus aspius</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Leuciscus aspius</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8120,7 +8120,7 @@
         <v>121090765</v>
       </c>
       <c r="B67" t="n">
-        <v>94497</v>
+        <v>94500</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121404558</v>
+        <v>121402734</v>
       </c>
       <c r="B68" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695865</v>
+        <v>696145</v>
       </c>
       <c r="R68" t="n">
-        <v>6603318</v>
+        <v>6603212</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8336,10 +8336,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121402402</v>
+        <v>121404898</v>
       </c>
       <c r="B69" t="n">
-        <v>57367</v>
+        <v>8424</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8348,31 +8348,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695942</v>
+        <v>696024</v>
       </c>
       <c r="R69" t="n">
-        <v>6603075</v>
+        <v>6603210</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8446,7 +8446,7 @@
         <v>121404293</v>
       </c>
       <c r="B70" t="n">
-        <v>5169</v>
+        <v>5172</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8550,10 +8550,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121404545</v>
+        <v>121402388</v>
       </c>
       <c r="B71" t="n">
-        <v>8432</v>
+        <v>57370</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8562,38 +8562,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695870</v>
+        <v>695971</v>
       </c>
       <c r="R71" t="n">
-        <v>6603295</v>
+        <v>6603090</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8652,10 +8657,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121404815</v>
+        <v>121404558</v>
       </c>
       <c r="B72" t="n">
-        <v>94497</v>
+        <v>57370</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8664,38 +8669,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695864</v>
+        <v>695865</v>
       </c>
       <c r="R72" t="n">
-        <v>6603266</v>
+        <v>6603318</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8725,9 +8735,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8742,22 +8762,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121402709</v>
+        <v>121404545</v>
       </c>
       <c r="B73" t="n">
-        <v>57367</v>
+        <v>8435</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8766,43 +8786,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696025</v>
+        <v>695870</v>
       </c>
       <c r="R73" t="n">
-        <v>6603166</v>
+        <v>6603295</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8861,10 +8876,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121402355</v>
+        <v>121405694</v>
       </c>
       <c r="B74" t="n">
-        <v>5189</v>
+        <v>98098</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8873,43 +8888,52 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696001</v>
+        <v>695999</v>
       </c>
       <c r="R74" t="n">
-        <v>6603109</v>
+        <v>6603117</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8939,9 +8963,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8956,22 +8995,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121402388</v>
+        <v>121404209</v>
       </c>
       <c r="B75" t="n">
-        <v>57367</v>
+        <v>94500</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8980,43 +9019,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695971</v>
+        <v>695935</v>
       </c>
       <c r="R75" t="n">
-        <v>6603090</v>
+        <v>6603415</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9075,10 +9109,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402734</v>
+        <v>121402402</v>
       </c>
       <c r="B76" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9111,19 +9145,19 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696145</v>
+        <v>695942</v>
       </c>
       <c r="R76" t="n">
-        <v>6603212</v>
+        <v>6603075</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9153,19 +9187,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9180,22 +9204,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121405386</v>
+        <v>121404815</v>
       </c>
       <c r="B77" t="n">
-        <v>90675</v>
+        <v>94500</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9208,34 +9232,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696099</v>
+        <v>695864</v>
       </c>
       <c r="R77" t="n">
-        <v>6603163</v>
+        <v>6603266</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9294,10 +9318,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402352</v>
+        <v>121402809</v>
       </c>
       <c r="B78" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9339,10 +9363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696013</v>
+        <v>696135</v>
       </c>
       <c r="R78" t="n">
-        <v>6603120</v>
+        <v>6603162</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9401,10 +9425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402404</v>
+        <v>121404569</v>
       </c>
       <c r="B79" t="n">
-        <v>5169</v>
+        <v>4775</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9417,21 +9441,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9442,14 +9466,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695942</v>
+        <v>695858</v>
       </c>
       <c r="R79" t="n">
-        <v>6603075</v>
+        <v>6603299</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9508,10 +9532,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121405694</v>
+        <v>121402355</v>
       </c>
       <c r="B80" t="n">
-        <v>98095</v>
+        <v>5192</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9520,52 +9544,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695999</v>
+        <v>696001</v>
       </c>
       <c r="R80" t="n">
-        <v>6603117</v>
+        <v>6603109</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9595,24 +9610,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9627,12 +9627,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
         <v>121403961</v>
       </c>
       <c r="B81" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9756,10 +9756,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404569</v>
+        <v>121404539</v>
       </c>
       <c r="B82" t="n">
-        <v>4772</v>
+        <v>57370</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9768,31 +9768,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695858</v>
+        <v>695869</v>
       </c>
       <c r="R82" t="n">
-        <v>6603299</v>
+        <v>6603281</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9863,10 +9863,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404249</v>
+        <v>121405386</v>
       </c>
       <c r="B83" t="n">
-        <v>57367</v>
+        <v>90678</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9875,43 +9875,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695896</v>
+        <v>696099</v>
       </c>
       <c r="R83" t="n">
-        <v>6603382</v>
+        <v>6603163</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9970,10 +9965,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404898</v>
+        <v>121404249</v>
       </c>
       <c r="B84" t="n">
-        <v>8421</v>
+        <v>57370</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9982,43 +9977,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696024</v>
+        <v>695896</v>
       </c>
       <c r="R84" t="n">
-        <v>6603210</v>
+        <v>6603382</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10077,10 +10072,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404209</v>
+        <v>121402404</v>
       </c>
       <c r="B85" t="n">
-        <v>94497</v>
+        <v>5172</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10093,34 +10088,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695935</v>
+        <v>695942</v>
       </c>
       <c r="R85" t="n">
-        <v>6603415</v>
+        <v>6603075</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
         <v>121404366</v>
       </c>
       <c r="B86" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10281,10 +10281,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121402809</v>
+        <v>121402709</v>
       </c>
       <c r="B87" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>696135</v>
+        <v>696025</v>
       </c>
       <c r="R87" t="n">
-        <v>6603162</v>
+        <v>6603166</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10388,10 +10388,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404539</v>
+        <v>121402352</v>
       </c>
       <c r="B88" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10429,14 +10429,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695869</v>
+        <v>696013</v>
       </c>
       <c r="R88" t="n">
-        <v>6603281</v>
+        <v>6603120</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121402734</v>
+        <v>121405386</v>
       </c>
       <c r="B68" t="n">
-        <v>57370</v>
+        <v>90678</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8231,43 +8231,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696145</v>
+        <v>696099</v>
       </c>
       <c r="R68" t="n">
-        <v>6603212</v>
+        <v>6603163</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8297,19 +8292,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8324,22 +8309,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121404898</v>
+        <v>121402388</v>
       </c>
       <c r="B69" t="n">
-        <v>8424</v>
+        <v>57370</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8348,43 +8333,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696024</v>
+        <v>695971</v>
       </c>
       <c r="R69" t="n">
-        <v>6603210</v>
+        <v>6603090</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8443,10 +8428,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121404293</v>
+        <v>121403961</v>
       </c>
       <c r="B70" t="n">
-        <v>5172</v>
+        <v>79688</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8455,43 +8440,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695856</v>
+        <v>695886</v>
       </c>
       <c r="R70" t="n">
-        <v>6603367</v>
+        <v>6603243</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8521,9 +8501,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8538,22 +8533,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121402388</v>
+        <v>121404209</v>
       </c>
       <c r="B71" t="n">
-        <v>57370</v>
+        <v>94500</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8562,43 +8557,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695971</v>
+        <v>695935</v>
       </c>
       <c r="R71" t="n">
-        <v>6603090</v>
+        <v>6603415</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8657,10 +8647,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121404558</v>
+        <v>121402404</v>
       </c>
       <c r="B72" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8669,43 +8659,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695865</v>
+        <v>695942</v>
       </c>
       <c r="R72" t="n">
-        <v>6603318</v>
+        <v>6603075</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8735,19 +8725,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8762,22 +8742,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121404545</v>
+        <v>121404898</v>
       </c>
       <c r="B73" t="n">
-        <v>8435</v>
+        <v>8424</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8790,34 +8770,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695870</v>
+        <v>696024</v>
       </c>
       <c r="R73" t="n">
-        <v>6603295</v>
+        <v>6603210</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8876,10 +8861,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121405694</v>
+        <v>121402734</v>
       </c>
       <c r="B74" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8888,40 +8873,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8930,10 +8906,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695999</v>
+        <v>696145</v>
       </c>
       <c r="R74" t="n">
-        <v>6603117</v>
+        <v>6603212</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8965,7 +8941,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8975,12 +8951,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9000,17 +8971,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121404209</v>
+        <v>121402809</v>
       </c>
       <c r="B75" t="n">
-        <v>94500</v>
+        <v>57370</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9019,38 +8990,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695935</v>
+        <v>696135</v>
       </c>
       <c r="R75" t="n">
-        <v>6603415</v>
+        <v>6603162</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9109,10 +9085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402402</v>
+        <v>121404545</v>
       </c>
       <c r="B76" t="n">
-        <v>57370</v>
+        <v>8435</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9121,43 +9097,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695942</v>
+        <v>695870</v>
       </c>
       <c r="R76" t="n">
-        <v>6603075</v>
+        <v>6603295</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9216,10 +9187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404815</v>
+        <v>121404558</v>
       </c>
       <c r="B77" t="n">
-        <v>94500</v>
+        <v>57370</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9228,38 +9199,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695864</v>
+        <v>695865</v>
       </c>
       <c r="R77" t="n">
-        <v>6603266</v>
+        <v>6603318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9289,9 +9265,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9306,19 +9292,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402809</v>
+        <v>121402402</v>
       </c>
       <c r="B78" t="n">
         <v>57370</v>
@@ -9354,7 +9340,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9363,10 +9349,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696135</v>
+        <v>695942</v>
       </c>
       <c r="R78" t="n">
-        <v>6603162</v>
+        <v>6603075</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9425,10 +9411,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404569</v>
+        <v>121404366</v>
       </c>
       <c r="B79" t="n">
-        <v>4775</v>
+        <v>90713</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9437,43 +9423,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695858</v>
+        <v>695857</v>
       </c>
       <c r="R79" t="n">
-        <v>6603299</v>
+        <v>6603366</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9639,10 +9620,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121403961</v>
+        <v>121404249</v>
       </c>
       <c r="B81" t="n">
-        <v>79688</v>
+        <v>57370</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9655,34 +9636,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695886</v>
+        <v>695896</v>
       </c>
       <c r="R81" t="n">
-        <v>6603243</v>
+        <v>6603382</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9712,24 +9698,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9744,19 +9715,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404539</v>
+        <v>121402709</v>
       </c>
       <c r="B82" t="n">
         <v>57370</v>
@@ -9797,14 +9768,14 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695869</v>
+        <v>696025</v>
       </c>
       <c r="R82" t="n">
-        <v>6603281</v>
+        <v>6603166</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9863,10 +9834,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121405386</v>
+        <v>121405694</v>
       </c>
       <c r="B83" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9875,38 +9846,52 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696099</v>
+        <v>695999</v>
       </c>
       <c r="R83" t="n">
-        <v>6603163</v>
+        <v>6603117</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9936,9 +9921,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9953,22 +9953,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404249</v>
+        <v>121404815</v>
       </c>
       <c r="B84" t="n">
-        <v>57370</v>
+        <v>94500</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9977,43 +9977,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695896</v>
+        <v>695864</v>
       </c>
       <c r="R84" t="n">
-        <v>6603382</v>
+        <v>6603266</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10072,10 +10067,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121402404</v>
+        <v>121402352</v>
       </c>
       <c r="B85" t="n">
-        <v>5172</v>
+        <v>57370</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10084,31 +10079,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10117,10 +10112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695942</v>
+        <v>696013</v>
       </c>
       <c r="R85" t="n">
-        <v>6603075</v>
+        <v>6603120</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10179,10 +10174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404366</v>
+        <v>121404539</v>
       </c>
       <c r="B86" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10195,34 +10190,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695857</v>
+        <v>695869</v>
       </c>
       <c r="R86" t="n">
-        <v>6603366</v>
+        <v>6603281</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10281,10 +10281,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121402709</v>
+        <v>121404569</v>
       </c>
       <c r="B87" t="n">
-        <v>57370</v>
+        <v>4775</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10293,43 +10293,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>696025</v>
+        <v>695858</v>
       </c>
       <c r="R87" t="n">
-        <v>6603166</v>
+        <v>6603299</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10388,10 +10388,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121402352</v>
+        <v>121404293</v>
       </c>
       <c r="B88" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10400,43 +10400,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696013</v>
+        <v>695856</v>
       </c>
       <c r="R88" t="n">
-        <v>6603120</v>
+        <v>6603367</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -9187,10 +9187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404558</v>
+        <v>121404366</v>
       </c>
       <c r="B77" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9203,39 +9203,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695865</v>
+        <v>695857</v>
       </c>
       <c r="R77" t="n">
-        <v>6603318</v>
+        <v>6603366</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9265,19 +9260,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9292,19 +9277,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402402</v>
+        <v>121404558</v>
       </c>
       <c r="B78" t="n">
         <v>57370</v>
@@ -9340,19 +9325,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695942</v>
+        <v>695865</v>
       </c>
       <c r="R78" t="n">
-        <v>6603075</v>
+        <v>6603318</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9382,9 +9367,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9399,22 +9394,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404366</v>
+        <v>121402402</v>
       </c>
       <c r="B79" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9427,34 +9422,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695857</v>
+        <v>695942</v>
       </c>
       <c r="R79" t="n">
-        <v>6603366</v>
+        <v>6603075</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9513,10 +9513,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402355</v>
+        <v>121404249</v>
       </c>
       <c r="B80" t="n">
-        <v>5192</v>
+        <v>57370</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9525,20 +9525,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9549,7 +9549,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9558,10 +9558,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696001</v>
+        <v>695896</v>
       </c>
       <c r="R80" t="n">
-        <v>6603109</v>
+        <v>6603382</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9620,7 +9620,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404249</v>
+        <v>121402709</v>
       </c>
       <c r="B81" t="n">
         <v>57370</v>
@@ -9661,14 +9661,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695896</v>
+        <v>696025</v>
       </c>
       <c r="R81" t="n">
-        <v>6603382</v>
+        <v>6603166</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9727,10 +9727,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121402709</v>
+        <v>121402355</v>
       </c>
       <c r="B82" t="n">
-        <v>57370</v>
+        <v>5192</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9739,20 +9739,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9763,19 +9763,19 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696025</v>
+        <v>696001</v>
       </c>
       <c r="R82" t="n">
-        <v>6603166</v>
+        <v>6603109</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9965,10 +9965,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404815</v>
+        <v>121402352</v>
       </c>
       <c r="B84" t="n">
-        <v>94500</v>
+        <v>57370</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9977,38 +9977,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695864</v>
+        <v>696013</v>
       </c>
       <c r="R84" t="n">
-        <v>6603266</v>
+        <v>6603120</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10067,10 +10072,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121402352</v>
+        <v>121404815</v>
       </c>
       <c r="B85" t="n">
-        <v>57370</v>
+        <v>94500</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10079,43 +10084,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696013</v>
+        <v>695864</v>
       </c>
       <c r="R85" t="n">
-        <v>6603120</v>
+        <v>6603266</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8428,10 +8428,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121403961</v>
+        <v>121404209</v>
       </c>
       <c r="B70" t="n">
-        <v>79688</v>
+        <v>94500</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8440,38 +8440,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695886</v>
+        <v>695935</v>
       </c>
       <c r="R70" t="n">
-        <v>6603243</v>
+        <v>6603415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8501,24 +8501,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8533,22 +8518,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121404209</v>
+        <v>121403961</v>
       </c>
       <c r="B71" t="n">
-        <v>94500</v>
+        <v>79688</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8557,38 +8542,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695935</v>
+        <v>695886</v>
       </c>
       <c r="R71" t="n">
-        <v>6603415</v>
+        <v>6603243</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8618,9 +8603,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8635,12 +8635,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8978,10 +8978,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121402809</v>
+        <v>121404545</v>
       </c>
       <c r="B75" t="n">
-        <v>57370</v>
+        <v>8435</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8990,43 +8990,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696135</v>
+        <v>695870</v>
       </c>
       <c r="R75" t="n">
-        <v>6603162</v>
+        <v>6603295</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9085,10 +9080,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404545</v>
+        <v>121402809</v>
       </c>
       <c r="B76" t="n">
-        <v>8435</v>
+        <v>57370</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9097,38 +9092,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695870</v>
+        <v>696135</v>
       </c>
       <c r="R76" t="n">
-        <v>6603295</v>
+        <v>6603162</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9187,10 +9187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404366</v>
+        <v>121404558</v>
       </c>
       <c r="B77" t="n">
-        <v>90713</v>
+        <v>57370</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9203,34 +9203,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695857</v>
+        <v>695865</v>
       </c>
       <c r="R77" t="n">
-        <v>6603366</v>
+        <v>6603318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9260,9 +9265,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9277,19 +9292,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404558</v>
+        <v>121402402</v>
       </c>
       <c r="B78" t="n">
         <v>57370</v>
@@ -9325,19 +9340,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695865</v>
+        <v>695942</v>
       </c>
       <c r="R78" t="n">
-        <v>6603318</v>
+        <v>6603075</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9367,19 +9382,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9394,22 +9399,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402402</v>
+        <v>121404366</v>
       </c>
       <c r="B79" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9422,39 +9427,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695942</v>
+        <v>695857</v>
       </c>
       <c r="R79" t="n">
-        <v>6603075</v>
+        <v>6603366</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9965,10 +9965,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402352</v>
+        <v>121404815</v>
       </c>
       <c r="B84" t="n">
-        <v>57370</v>
+        <v>94500</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9977,43 +9977,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696013</v>
+        <v>695864</v>
       </c>
       <c r="R84" t="n">
-        <v>6603120</v>
+        <v>6603266</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10072,10 +10067,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404815</v>
+        <v>121402352</v>
       </c>
       <c r="B85" t="n">
-        <v>94500</v>
+        <v>57370</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10084,38 +10079,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695864</v>
+        <v>696013</v>
       </c>
       <c r="R85" t="n">
-        <v>6603266</v>
+        <v>6603120</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404539</v>
+        <v>121404569</v>
       </c>
       <c r="B86" t="n">
-        <v>57370</v>
+        <v>4775</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10186,31 +10186,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695869</v>
+        <v>695858</v>
       </c>
       <c r="R86" t="n">
-        <v>6603281</v>
+        <v>6603299</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10281,10 +10281,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404569</v>
+        <v>121404539</v>
       </c>
       <c r="B87" t="n">
-        <v>4775</v>
+        <v>57370</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10293,31 +10293,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695858</v>
+        <v>695869</v>
       </c>
       <c r="R87" t="n">
-        <v>6603299</v>
+        <v>6603281</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121405386</v>
+        <v>121402809</v>
       </c>
       <c r="B68" t="n">
-        <v>90678</v>
+        <v>57371</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8231,38 +8231,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696099</v>
+        <v>696135</v>
       </c>
       <c r="R68" t="n">
-        <v>6603163</v>
+        <v>6603162</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8321,10 +8326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121402388</v>
+        <v>121405386</v>
       </c>
       <c r="B69" t="n">
-        <v>57370</v>
+        <v>90684</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8333,43 +8338,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695971</v>
+        <v>696099</v>
       </c>
       <c r="R69" t="n">
-        <v>6603090</v>
+        <v>6603163</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8428,10 +8428,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121404209</v>
+        <v>121402352</v>
       </c>
       <c r="B70" t="n">
-        <v>94500</v>
+        <v>57371</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8440,38 +8440,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695935</v>
+        <v>696013</v>
       </c>
       <c r="R70" t="n">
-        <v>6603415</v>
+        <v>6603120</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8530,10 +8535,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121403961</v>
+        <v>121404545</v>
       </c>
       <c r="B71" t="n">
-        <v>79688</v>
+        <v>8435</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8542,38 +8547,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695886</v>
+        <v>695870</v>
       </c>
       <c r="R71" t="n">
-        <v>6603243</v>
+        <v>6603295</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8603,24 +8608,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8635,22 +8625,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121402404</v>
+        <v>121402709</v>
       </c>
       <c r="B72" t="n">
-        <v>5172</v>
+        <v>57371</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8659,31 +8649,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8692,10 +8682,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695942</v>
+        <v>696025</v>
       </c>
       <c r="R72" t="n">
-        <v>6603075</v>
+        <v>6603166</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8861,10 +8851,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121402734</v>
+        <v>121404539</v>
       </c>
       <c r="B74" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8897,19 +8887,19 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696145</v>
+        <v>695869</v>
       </c>
       <c r="R74" t="n">
-        <v>6603212</v>
+        <v>6603281</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8939,19 +8929,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8966,22 +8946,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121404545</v>
+        <v>121403961</v>
       </c>
       <c r="B75" t="n">
-        <v>8435</v>
+        <v>79689</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8990,38 +8970,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695870</v>
+        <v>695886</v>
       </c>
       <c r="R75" t="n">
-        <v>6603295</v>
+        <v>6603243</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9051,9 +9031,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9068,22 +9063,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402809</v>
+        <v>121404569</v>
       </c>
       <c r="B76" t="n">
-        <v>57370</v>
+        <v>4775</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9092,43 +9087,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696135</v>
+        <v>695858</v>
       </c>
       <c r="R76" t="n">
-        <v>6603162</v>
+        <v>6603299</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9190,7 +9185,7 @@
         <v>121404558</v>
       </c>
       <c r="B77" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9304,10 +9299,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402402</v>
+        <v>121402388</v>
       </c>
       <c r="B78" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9345,14 +9340,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695942</v>
+        <v>695971</v>
       </c>
       <c r="R78" t="n">
-        <v>6603075</v>
+        <v>6603090</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9411,10 +9406,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404366</v>
+        <v>121402734</v>
       </c>
       <c r="B79" t="n">
-        <v>90713</v>
+        <v>57371</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9427,34 +9422,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695857</v>
+        <v>696145</v>
       </c>
       <c r="R79" t="n">
-        <v>6603366</v>
+        <v>6603212</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9484,9 +9484,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9501,22 +9511,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121404249</v>
+        <v>121404366</v>
       </c>
       <c r="B80" t="n">
-        <v>57370</v>
+        <v>90719</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9529,39 +9539,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695896</v>
+        <v>695857</v>
       </c>
       <c r="R80" t="n">
-        <v>6603382</v>
+        <v>6603366</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9620,10 +9625,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121402709</v>
+        <v>121402404</v>
       </c>
       <c r="B81" t="n">
-        <v>57370</v>
+        <v>5172</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9632,31 +9637,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9665,10 +9670,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696025</v>
+        <v>695942</v>
       </c>
       <c r="R81" t="n">
-        <v>6603166</v>
+        <v>6603075</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9727,10 +9732,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121402355</v>
+        <v>121404209</v>
       </c>
       <c r="B82" t="n">
-        <v>5192</v>
+        <v>94506</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9743,39 +9748,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>105930</v>
+        <v>2809</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696001</v>
+        <v>695935</v>
       </c>
       <c r="R82" t="n">
-        <v>6603109</v>
+        <v>6603415</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9834,10 +9834,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121405694</v>
+        <v>121404293</v>
       </c>
       <c r="B83" t="n">
-        <v>98098</v>
+        <v>5172</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9846,52 +9846,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695999</v>
+        <v>695856</v>
       </c>
       <c r="R83" t="n">
-        <v>6603117</v>
+        <v>6603367</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9921,24 +9912,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9953,22 +9929,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404815</v>
+        <v>121402355</v>
       </c>
       <c r="B84" t="n">
-        <v>94500</v>
+        <v>5192</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9981,34 +9957,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2809</v>
+        <v>105930</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695864</v>
+        <v>696001</v>
       </c>
       <c r="R84" t="n">
-        <v>6603266</v>
+        <v>6603109</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10067,10 +10048,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121402352</v>
+        <v>121404815</v>
       </c>
       <c r="B85" t="n">
-        <v>57370</v>
+        <v>94506</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10079,43 +10060,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696013</v>
+        <v>695864</v>
       </c>
       <c r="R85" t="n">
-        <v>6603120</v>
+        <v>6603266</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10174,10 +10150,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404569</v>
+        <v>121404249</v>
       </c>
       <c r="B86" t="n">
-        <v>4775</v>
+        <v>57371</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10186,31 +10162,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10219,10 +10195,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695858</v>
+        <v>695896</v>
       </c>
       <c r="R86" t="n">
-        <v>6603299</v>
+        <v>6603382</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10281,10 +10257,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404539</v>
+        <v>121402402</v>
       </c>
       <c r="B87" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10317,19 +10293,19 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695869</v>
+        <v>695942</v>
       </c>
       <c r="R87" t="n">
-        <v>6603281</v>
+        <v>6603075</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10388,10 +10364,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404293</v>
+        <v>121405694</v>
       </c>
       <c r="B88" t="n">
-        <v>5172</v>
+        <v>98104</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10400,43 +10376,52 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695856</v>
+        <v>695999</v>
       </c>
       <c r="R88" t="n">
-        <v>6603367</v>
+        <v>6603117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10466,9 +10451,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10483,12 +10483,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121402809</v>
+        <v>121402709</v>
       </c>
       <c r="B68" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696135</v>
+        <v>696025</v>
       </c>
       <c r="R68" t="n">
-        <v>6603162</v>
+        <v>6603166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121405386</v>
+        <v>121404293</v>
       </c>
       <c r="B69" t="n">
-        <v>90684</v>
+        <v>5172</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8342,34 +8342,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696099</v>
+        <v>695856</v>
       </c>
       <c r="R69" t="n">
-        <v>6603163</v>
+        <v>6603367</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8428,10 +8433,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121402352</v>
+        <v>121404249</v>
       </c>
       <c r="B70" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8469,14 +8474,14 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696013</v>
+        <v>695896</v>
       </c>
       <c r="R70" t="n">
-        <v>6603120</v>
+        <v>6603382</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8535,10 +8540,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121404545</v>
+        <v>121402388</v>
       </c>
       <c r="B71" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8547,38 +8552,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695870</v>
+        <v>695971</v>
       </c>
       <c r="R71" t="n">
-        <v>6603295</v>
+        <v>6603090</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8637,10 +8647,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121402709</v>
+        <v>121402734</v>
       </c>
       <c r="B72" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8673,19 +8683,19 @@
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696025</v>
+        <v>696145</v>
       </c>
       <c r="R72" t="n">
-        <v>6603166</v>
+        <v>6603212</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8715,9 +8725,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8732,22 +8752,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121404898</v>
+        <v>121402402</v>
       </c>
       <c r="B73" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8756,31 +8776,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8789,10 +8809,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696024</v>
+        <v>695942</v>
       </c>
       <c r="R73" t="n">
-        <v>6603210</v>
+        <v>6603075</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8851,10 +8871,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121404539</v>
+        <v>121404569</v>
       </c>
       <c r="B74" t="n">
-        <v>57371</v>
+        <v>4775</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8863,31 +8883,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8896,10 +8916,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695869</v>
+        <v>695858</v>
       </c>
       <c r="R74" t="n">
-        <v>6603281</v>
+        <v>6603299</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8958,10 +8978,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121403961</v>
+        <v>121402404</v>
       </c>
       <c r="B75" t="n">
-        <v>79689</v>
+        <v>5172</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8970,38 +8990,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695886</v>
+        <v>695942</v>
       </c>
       <c r="R75" t="n">
-        <v>6603243</v>
+        <v>6603075</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9031,24 +9056,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9063,22 +9073,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404569</v>
+        <v>121402355</v>
       </c>
       <c r="B76" t="n">
-        <v>4775</v>
+        <v>5192</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9091,21 +9101,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9120,10 +9130,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695858</v>
+        <v>696001</v>
       </c>
       <c r="R76" t="n">
-        <v>6603299</v>
+        <v>6603109</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9182,10 +9192,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404558</v>
+        <v>121403961</v>
       </c>
       <c r="B77" t="n">
-        <v>57371</v>
+        <v>79690</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9198,39 +9208,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695865</v>
+        <v>695886</v>
       </c>
       <c r="R77" t="n">
-        <v>6603318</v>
+        <v>6603243</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9262,7 +9267,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9272,7 +9277,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9292,17 +9302,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402388</v>
+        <v>121404539</v>
       </c>
       <c r="B78" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9335,7 +9345,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9344,10 +9354,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695971</v>
+        <v>695869</v>
       </c>
       <c r="R78" t="n">
-        <v>6603090</v>
+        <v>6603281</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9406,10 +9416,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402734</v>
+        <v>121404558</v>
       </c>
       <c r="B79" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9442,7 +9452,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9451,10 +9461,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696145</v>
+        <v>695865</v>
       </c>
       <c r="R79" t="n">
-        <v>6603212</v>
+        <v>6603318</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9486,7 +9496,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9496,7 +9506,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9523,10 +9533,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121404366</v>
+        <v>121405386</v>
       </c>
       <c r="B80" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9535,38 +9545,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695857</v>
+        <v>696099</v>
       </c>
       <c r="R80" t="n">
-        <v>6603366</v>
+        <v>6603163</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9625,10 +9635,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121402404</v>
+        <v>121404815</v>
       </c>
       <c r="B81" t="n">
-        <v>5172</v>
+        <v>94507</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9641,39 +9651,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100526</v>
+        <v>2809</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695942</v>
+        <v>695864</v>
       </c>
       <c r="R81" t="n">
-        <v>6603075</v>
+        <v>6603266</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9732,10 +9737,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404209</v>
+        <v>121404545</v>
       </c>
       <c r="B82" t="n">
-        <v>94506</v>
+        <v>8435</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9748,34 +9753,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2809</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695935</v>
+        <v>695870</v>
       </c>
       <c r="R82" t="n">
-        <v>6603415</v>
+        <v>6603295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9834,10 +9839,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404293</v>
+        <v>121402352</v>
       </c>
       <c r="B83" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9846,43 +9851,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695856</v>
+        <v>696013</v>
       </c>
       <c r="R83" t="n">
-        <v>6603367</v>
+        <v>6603120</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9941,10 +9946,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402355</v>
+        <v>121402809</v>
       </c>
       <c r="B84" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9953,20 +9958,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9977,19 +9982,19 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696001</v>
+        <v>696135</v>
       </c>
       <c r="R84" t="n">
-        <v>6603109</v>
+        <v>6603162</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10048,10 +10053,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404815</v>
+        <v>121405694</v>
       </c>
       <c r="B85" t="n">
-        <v>94506</v>
+        <v>98105</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10060,38 +10065,52 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695864</v>
+        <v>695999</v>
       </c>
       <c r="R85" t="n">
-        <v>6603266</v>
+        <v>6603117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10121,9 +10140,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10138,22 +10172,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404249</v>
+        <v>121404366</v>
       </c>
       <c r="B86" t="n">
-        <v>57371</v>
+        <v>90720</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10166,39 +10200,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695896</v>
+        <v>695857</v>
       </c>
       <c r="R86" t="n">
-        <v>6603382</v>
+        <v>6603366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10257,10 +10286,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121402402</v>
+        <v>121404209</v>
       </c>
       <c r="B87" t="n">
-        <v>57371</v>
+        <v>94507</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10269,43 +10298,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695942</v>
+        <v>695935</v>
       </c>
       <c r="R87" t="n">
-        <v>6603075</v>
+        <v>6603415</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10364,10 +10388,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121405694</v>
+        <v>121404898</v>
       </c>
       <c r="B88" t="n">
-        <v>98104</v>
+        <v>8424</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10376,52 +10400,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695999</v>
+        <v>696024</v>
       </c>
       <c r="R88" t="n">
-        <v>6603117</v>
+        <v>6603210</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10451,24 +10466,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10483,12 +10483,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121402709</v>
+        <v>121402355</v>
       </c>
       <c r="B68" t="n">
-        <v>57372</v>
+        <v>5192</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8231,20 +8231,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8255,19 +8255,19 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696025</v>
+        <v>696001</v>
       </c>
       <c r="R68" t="n">
-        <v>6603166</v>
+        <v>6603109</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121404293</v>
+        <v>121404569</v>
       </c>
       <c r="B69" t="n">
-        <v>5172</v>
+        <v>4775</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8342,21 +8342,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695856</v>
+        <v>695858</v>
       </c>
       <c r="R69" t="n">
-        <v>6603367</v>
+        <v>6603299</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121404249</v>
+        <v>121404293</v>
       </c>
       <c r="B70" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8445,31 +8445,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695896</v>
+        <v>695856</v>
       </c>
       <c r="R70" t="n">
-        <v>6603382</v>
+        <v>6603367</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8540,7 +8540,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121402388</v>
+        <v>121402734</v>
       </c>
       <c r="B71" t="n">
         <v>57372</v>
@@ -8576,19 +8576,19 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695971</v>
+        <v>696145</v>
       </c>
       <c r="R71" t="n">
-        <v>6603090</v>
+        <v>6603212</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8618,9 +8618,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8635,22 +8645,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121402734</v>
+        <v>121404545</v>
       </c>
       <c r="B72" t="n">
-        <v>57372</v>
+        <v>8435</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8659,43 +8669,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696145</v>
+        <v>695870</v>
       </c>
       <c r="R72" t="n">
-        <v>6603212</v>
+        <v>6603295</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8725,19 +8730,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8752,22 +8747,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121402402</v>
+        <v>121405386</v>
       </c>
       <c r="B73" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8776,43 +8771,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695942</v>
+        <v>696099</v>
       </c>
       <c r="R73" t="n">
-        <v>6603075</v>
+        <v>6603163</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8871,10 +8861,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121404569</v>
+        <v>121404815</v>
       </c>
       <c r="B74" t="n">
-        <v>4775</v>
+        <v>94507</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8887,39 +8877,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102306</v>
+        <v>2809</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695858</v>
+        <v>695864</v>
       </c>
       <c r="R74" t="n">
-        <v>6603299</v>
+        <v>6603266</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8978,10 +8963,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121402404</v>
+        <v>121403961</v>
       </c>
       <c r="B75" t="n">
-        <v>5172</v>
+        <v>79690</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8990,43 +8975,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695942</v>
+        <v>695886</v>
       </c>
       <c r="R75" t="n">
-        <v>6603075</v>
+        <v>6603243</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9056,9 +9036,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9073,22 +9068,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402355</v>
+        <v>121402388</v>
       </c>
       <c r="B76" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9097,20 +9092,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9121,7 +9116,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9130,10 +9125,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696001</v>
+        <v>695971</v>
       </c>
       <c r="R76" t="n">
-        <v>6603109</v>
+        <v>6603090</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9192,10 +9187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121403961</v>
+        <v>121404558</v>
       </c>
       <c r="B77" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9208,34 +9203,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695886</v>
+        <v>695865</v>
       </c>
       <c r="R77" t="n">
-        <v>6603243</v>
+        <v>6603318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9277,12 +9277,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9302,14 +9297,14 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121404539</v>
+        <v>121402352</v>
       </c>
       <c r="B78" t="n">
         <v>57372</v>
@@ -9350,14 +9345,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695869</v>
+        <v>696013</v>
       </c>
       <c r="R78" t="n">
-        <v>6603281</v>
+        <v>6603120</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9416,10 +9411,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404558</v>
+        <v>121405694</v>
       </c>
       <c r="B79" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9428,31 +9423,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9461,10 +9465,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695865</v>
+        <v>695999</v>
       </c>
       <c r="R79" t="n">
-        <v>6603318</v>
+        <v>6603117</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9496,7 +9500,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9506,7 +9510,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9526,17 +9535,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121405386</v>
+        <v>121402402</v>
       </c>
       <c r="B80" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9545,38 +9554,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696099</v>
+        <v>695942</v>
       </c>
       <c r="R80" t="n">
-        <v>6603163</v>
+        <v>6603075</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9635,10 +9649,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404815</v>
+        <v>121404898</v>
       </c>
       <c r="B81" t="n">
-        <v>94507</v>
+        <v>8424</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9651,34 +9665,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2809</v>
+        <v>106554</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695864</v>
+        <v>696024</v>
       </c>
       <c r="R81" t="n">
-        <v>6603266</v>
+        <v>6603210</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9737,10 +9756,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404545</v>
+        <v>121402809</v>
       </c>
       <c r="B82" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9749,38 +9768,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695870</v>
+        <v>696135</v>
       </c>
       <c r="R82" t="n">
-        <v>6603295</v>
+        <v>6603162</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9839,10 +9863,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121402352</v>
+        <v>121404209</v>
       </c>
       <c r="B83" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9851,43 +9875,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696013</v>
+        <v>695935</v>
       </c>
       <c r="R83" t="n">
-        <v>6603120</v>
+        <v>6603415</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9946,10 +9965,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402809</v>
+        <v>121404366</v>
       </c>
       <c r="B84" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9962,39 +9981,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696135</v>
+        <v>695857</v>
       </c>
       <c r="R84" t="n">
-        <v>6603162</v>
+        <v>6603366</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10053,10 +10067,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121405694</v>
+        <v>121404539</v>
       </c>
       <c r="B85" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10065,52 +10079,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695999</v>
+        <v>695869</v>
       </c>
       <c r="R85" t="n">
-        <v>6603117</v>
+        <v>6603281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,24 +10145,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,22 +10162,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404366</v>
+        <v>121404249</v>
       </c>
       <c r="B86" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10200,34 +10190,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695857</v>
+        <v>695896</v>
       </c>
       <c r="R86" t="n">
-        <v>6603366</v>
+        <v>6603382</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10286,10 +10281,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404209</v>
+        <v>121402404</v>
       </c>
       <c r="B87" t="n">
-        <v>94507</v>
+        <v>5172</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10302,34 +10297,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695935</v>
+        <v>695942</v>
       </c>
       <c r="R87" t="n">
-        <v>6603415</v>
+        <v>6603075</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10388,10 +10388,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121404898</v>
+        <v>121402709</v>
       </c>
       <c r="B88" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10400,31 +10400,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696024</v>
+        <v>696025</v>
       </c>
       <c r="R88" t="n">
-        <v>6603210</v>
+        <v>6603166</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121402355</v>
+        <v>121402809</v>
       </c>
       <c r="B68" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8231,20 +8231,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8255,19 +8255,19 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696001</v>
+        <v>696135</v>
       </c>
       <c r="R68" t="n">
-        <v>6603109</v>
+        <v>6603162</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121404569</v>
+        <v>121404558</v>
       </c>
       <c r="B69" t="n">
-        <v>4775</v>
+        <v>57372</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8338,43 +8338,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695858</v>
+        <v>695865</v>
       </c>
       <c r="R69" t="n">
-        <v>6603299</v>
+        <v>6603318</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8404,9 +8404,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8421,22 +8431,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121404293</v>
+        <v>121402734</v>
       </c>
       <c r="B70" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8445,43 +8455,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695856</v>
+        <v>696145</v>
       </c>
       <c r="R70" t="n">
-        <v>6603367</v>
+        <v>6603212</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8511,9 +8521,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8528,22 +8548,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121402734</v>
+        <v>121405694</v>
       </c>
       <c r="B71" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8552,31 +8572,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8585,10 +8614,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696145</v>
+        <v>695999</v>
       </c>
       <c r="R71" t="n">
-        <v>6603212</v>
+        <v>6603117</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8620,7 +8649,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8630,7 +8659,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8650,17 +8684,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121404545</v>
+        <v>121402709</v>
       </c>
       <c r="B72" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8669,38 +8703,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695870</v>
+        <v>696025</v>
       </c>
       <c r="R72" t="n">
-        <v>6603295</v>
+        <v>6603166</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8759,10 +8798,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121405386</v>
+        <v>121402355</v>
       </c>
       <c r="B73" t="n">
-        <v>90685</v>
+        <v>5192</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8775,34 +8814,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696099</v>
+        <v>696001</v>
       </c>
       <c r="R73" t="n">
-        <v>6603163</v>
+        <v>6603109</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8861,10 +8905,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121404815</v>
+        <v>121404249</v>
       </c>
       <c r="B74" t="n">
-        <v>94507</v>
+        <v>57372</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8873,38 +8917,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695864</v>
+        <v>695896</v>
       </c>
       <c r="R74" t="n">
-        <v>6603266</v>
+        <v>6603382</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8963,10 +9012,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121403961</v>
+        <v>121404545</v>
       </c>
       <c r="B75" t="n">
-        <v>79690</v>
+        <v>8435</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8975,38 +9024,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695886</v>
+        <v>695870</v>
       </c>
       <c r="R75" t="n">
-        <v>6603243</v>
+        <v>6603295</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9036,24 +9085,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9068,19 +9102,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402388</v>
+        <v>121404539</v>
       </c>
       <c r="B76" t="n">
         <v>57372</v>
@@ -9116,7 +9150,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9125,10 +9159,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695971</v>
+        <v>695869</v>
       </c>
       <c r="R76" t="n">
-        <v>6603090</v>
+        <v>6603281</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9187,10 +9221,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404558</v>
+        <v>121402404</v>
       </c>
       <c r="B77" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9199,43 +9233,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695865</v>
+        <v>695942</v>
       </c>
       <c r="R77" t="n">
-        <v>6603318</v>
+        <v>6603075</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9265,19 +9299,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9292,22 +9316,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402352</v>
+        <v>121405386</v>
       </c>
       <c r="B78" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9316,43 +9340,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696013</v>
+        <v>696099</v>
       </c>
       <c r="R78" t="n">
-        <v>6603120</v>
+        <v>6603163</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9411,10 +9430,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121405694</v>
+        <v>121404569</v>
       </c>
       <c r="B79" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9423,52 +9442,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695999</v>
+        <v>695858</v>
       </c>
       <c r="R79" t="n">
-        <v>6603117</v>
+        <v>6603299</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9498,24 +9508,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9530,22 +9525,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121402402</v>
+        <v>121404898</v>
       </c>
       <c r="B80" t="n">
-        <v>57372</v>
+        <v>8424</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9554,31 +9549,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9587,10 +9582,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695942</v>
+        <v>696024</v>
       </c>
       <c r="R80" t="n">
-        <v>6603075</v>
+        <v>6603210</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9649,10 +9644,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121404898</v>
+        <v>121402352</v>
       </c>
       <c r="B81" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9661,31 +9656,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9694,10 +9689,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696024</v>
+        <v>696013</v>
       </c>
       <c r="R81" t="n">
-        <v>6603210</v>
+        <v>6603120</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9756,10 +9751,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121402809</v>
+        <v>121403961</v>
       </c>
       <c r="B82" t="n">
-        <v>57372</v>
+        <v>79690</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9772,39 +9767,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696135</v>
+        <v>695886</v>
       </c>
       <c r="R82" t="n">
-        <v>6603162</v>
+        <v>6603243</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9834,9 +9824,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9851,22 +9856,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404209</v>
+        <v>121404293</v>
       </c>
       <c r="B83" t="n">
-        <v>94507</v>
+        <v>5172</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9879,34 +9884,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695935</v>
+        <v>695856</v>
       </c>
       <c r="R83" t="n">
-        <v>6603415</v>
+        <v>6603367</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9965,10 +9975,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404366</v>
+        <v>121402402</v>
       </c>
       <c r="B84" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9981,34 +9991,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695857</v>
+        <v>695942</v>
       </c>
       <c r="R84" t="n">
-        <v>6603366</v>
+        <v>6603075</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10067,10 +10082,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404539</v>
+        <v>121404815</v>
       </c>
       <c r="B85" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10079,43 +10094,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695869</v>
+        <v>695864</v>
       </c>
       <c r="R85" t="n">
-        <v>6603281</v>
+        <v>6603266</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10174,10 +10184,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404249</v>
+        <v>121404209</v>
       </c>
       <c r="B86" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10186,43 +10196,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695896</v>
+        <v>695935</v>
       </c>
       <c r="R86" t="n">
-        <v>6603382</v>
+        <v>6603415</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10281,10 +10286,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121402404</v>
+        <v>121404366</v>
       </c>
       <c r="B87" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10293,43 +10298,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695942</v>
+        <v>695857</v>
       </c>
       <c r="R87" t="n">
-        <v>6603075</v>
+        <v>6603366</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10388,7 +10388,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121402709</v>
+        <v>121402388</v>
       </c>
       <c r="B88" t="n">
         <v>57372</v>
@@ -10424,19 +10424,19 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696025</v>
+        <v>695971</v>
       </c>
       <c r="R88" t="n">
-        <v>6603166</v>
+        <v>6603090</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8219,7 +8219,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121402809</v>
+        <v>121404539</v>
       </c>
       <c r="B68" t="n">
         <v>57372</v>
@@ -8260,14 +8260,14 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696135</v>
+        <v>695869</v>
       </c>
       <c r="R68" t="n">
-        <v>6603162</v>
+        <v>6603281</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121404558</v>
+        <v>121402352</v>
       </c>
       <c r="B69" t="n">
         <v>57372</v>
@@ -8362,19 +8362,19 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695865</v>
+        <v>696013</v>
       </c>
       <c r="R69" t="n">
-        <v>6603318</v>
+        <v>6603120</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8404,19 +8404,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8431,22 +8421,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121402734</v>
+        <v>121402404</v>
       </c>
       <c r="B70" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8455,43 +8445,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696145</v>
+        <v>695942</v>
       </c>
       <c r="R70" t="n">
-        <v>6603212</v>
+        <v>6603075</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8521,19 +8511,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8548,22 +8528,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121405694</v>
+        <v>121404898</v>
       </c>
       <c r="B71" t="n">
-        <v>98105</v>
+        <v>8424</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8572,52 +8552,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695999</v>
+        <v>696024</v>
       </c>
       <c r="R71" t="n">
-        <v>6603117</v>
+        <v>6603210</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8647,24 +8618,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8679,22 +8635,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121402709</v>
+        <v>121404815</v>
       </c>
       <c r="B72" t="n">
-        <v>57372</v>
+        <v>94507</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8703,43 +8659,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696025</v>
+        <v>695864</v>
       </c>
       <c r="R72" t="n">
-        <v>6603166</v>
+        <v>6603266</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8798,10 +8749,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121402355</v>
+        <v>121402809</v>
       </c>
       <c r="B73" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8810,20 +8761,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8834,19 +8785,19 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696001</v>
+        <v>696135</v>
       </c>
       <c r="R73" t="n">
-        <v>6603109</v>
+        <v>6603162</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8905,10 +8856,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121404249</v>
+        <v>121405386</v>
       </c>
       <c r="B74" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8917,43 +8868,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695896</v>
+        <v>696099</v>
       </c>
       <c r="R74" t="n">
-        <v>6603382</v>
+        <v>6603163</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9012,10 +8958,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121404545</v>
+        <v>121402709</v>
       </c>
       <c r="B75" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9024,38 +8970,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695870</v>
+        <v>696025</v>
       </c>
       <c r="R75" t="n">
-        <v>6603295</v>
+        <v>6603166</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9114,10 +9065,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404539</v>
+        <v>121404569</v>
       </c>
       <c r="B76" t="n">
-        <v>57372</v>
+        <v>4775</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9126,31 +9077,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9159,10 +9110,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695869</v>
+        <v>695858</v>
       </c>
       <c r="R76" t="n">
-        <v>6603281</v>
+        <v>6603299</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9221,10 +9172,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121402404</v>
+        <v>121404366</v>
       </c>
       <c r="B77" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9233,43 +9184,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695942</v>
+        <v>695857</v>
       </c>
       <c r="R77" t="n">
-        <v>6603075</v>
+        <v>6603366</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9328,10 +9274,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121405386</v>
+        <v>121402734</v>
       </c>
       <c r="B78" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9340,38 +9286,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696099</v>
+        <v>696145</v>
       </c>
       <c r="R78" t="n">
-        <v>6603163</v>
+        <v>6603212</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9401,9 +9352,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9418,22 +9379,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404569</v>
+        <v>121402355</v>
       </c>
       <c r="B79" t="n">
-        <v>4775</v>
+        <v>5192</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9446,21 +9407,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9475,10 +9436,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695858</v>
+        <v>696001</v>
       </c>
       <c r="R79" t="n">
-        <v>6603299</v>
+        <v>6603109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9537,10 +9498,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121404898</v>
+        <v>121405694</v>
       </c>
       <c r="B80" t="n">
-        <v>8424</v>
+        <v>98105</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9549,43 +9510,52 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696024</v>
+        <v>695999</v>
       </c>
       <c r="R80" t="n">
-        <v>6603210</v>
+        <v>6603117</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9615,9 +9585,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9632,19 +9617,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121402352</v>
+        <v>121402388</v>
       </c>
       <c r="B81" t="n">
         <v>57372</v>
@@ -9680,19 +9665,19 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696013</v>
+        <v>695971</v>
       </c>
       <c r="R81" t="n">
-        <v>6603120</v>
+        <v>6603090</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9751,10 +9736,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121403961</v>
+        <v>121404209</v>
       </c>
       <c r="B82" t="n">
-        <v>79690</v>
+        <v>94507</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9763,38 +9748,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695886</v>
+        <v>695935</v>
       </c>
       <c r="R82" t="n">
-        <v>6603243</v>
+        <v>6603415</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9824,24 +9809,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9856,22 +9826,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404293</v>
+        <v>121404249</v>
       </c>
       <c r="B83" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9880,31 +9850,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9913,10 +9883,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695856</v>
+        <v>695896</v>
       </c>
       <c r="R83" t="n">
-        <v>6603367</v>
+        <v>6603382</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9975,7 +9945,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121402402</v>
+        <v>121404558</v>
       </c>
       <c r="B84" t="n">
         <v>57372</v>
@@ -10011,19 +9981,19 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695942</v>
+        <v>695865</v>
       </c>
       <c r="R84" t="n">
-        <v>6603075</v>
+        <v>6603318</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10053,9 +10023,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10070,22 +10050,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404815</v>
+        <v>121404293</v>
       </c>
       <c r="B85" t="n">
-        <v>94507</v>
+        <v>5172</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10098,34 +10078,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695864</v>
+        <v>695856</v>
       </c>
       <c r="R85" t="n">
-        <v>6603266</v>
+        <v>6603367</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10184,10 +10169,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121404209</v>
+        <v>121403961</v>
       </c>
       <c r="B86" t="n">
-        <v>94507</v>
+        <v>79690</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10196,38 +10181,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695935</v>
+        <v>695886</v>
       </c>
       <c r="R86" t="n">
-        <v>6603415</v>
+        <v>6603243</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10257,9 +10242,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10274,22 +10274,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404366</v>
+        <v>121404545</v>
       </c>
       <c r="B87" t="n">
-        <v>90720</v>
+        <v>8435</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10298,25 +10298,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695857</v>
+        <v>695870</v>
       </c>
       <c r="R87" t="n">
-        <v>6603366</v>
+        <v>6603295</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10388,7 +10388,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121402388</v>
+        <v>121402402</v>
       </c>
       <c r="B88" t="n">
         <v>57372</v>
@@ -10429,14 +10429,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695971</v>
+        <v>695942</v>
       </c>
       <c r="R88" t="n">
-        <v>6603090</v>
+        <v>6603075</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -9172,10 +9172,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404366</v>
+        <v>121402734</v>
       </c>
       <c r="B77" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9188,34 +9188,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695857</v>
+        <v>696145</v>
       </c>
       <c r="R77" t="n">
-        <v>6603366</v>
+        <v>6603212</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9245,9 +9250,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9262,22 +9277,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402734</v>
+        <v>121402355</v>
       </c>
       <c r="B78" t="n">
-        <v>57372</v>
+        <v>5192</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9286,20 +9301,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9310,19 +9325,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696145</v>
+        <v>696001</v>
       </c>
       <c r="R78" t="n">
-        <v>6603212</v>
+        <v>6603109</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9352,19 +9367,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9379,22 +9384,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402355</v>
+        <v>121404366</v>
       </c>
       <c r="B79" t="n">
-        <v>5192</v>
+        <v>90720</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9403,43 +9408,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696001</v>
+        <v>695857</v>
       </c>
       <c r="R79" t="n">
-        <v>6603109</v>
+        <v>6603366</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -9172,10 +9172,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121402734</v>
+        <v>121404366</v>
       </c>
       <c r="B77" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9188,39 +9188,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696145</v>
+        <v>695857</v>
       </c>
       <c r="R77" t="n">
-        <v>6603212</v>
+        <v>6603366</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9250,19 +9245,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9277,22 +9262,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402355</v>
+        <v>121402734</v>
       </c>
       <c r="B78" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9301,20 +9286,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9325,19 +9310,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696001</v>
+        <v>696145</v>
       </c>
       <c r="R78" t="n">
-        <v>6603109</v>
+        <v>6603212</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9367,9 +9352,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9384,22 +9379,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121404366</v>
+        <v>121402355</v>
       </c>
       <c r="B79" t="n">
-        <v>90720</v>
+        <v>5192</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9408,38 +9403,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695857</v>
+        <v>696001</v>
       </c>
       <c r="R79" t="n">
-        <v>6603366</v>
+        <v>6603109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8219,10 +8219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121404539</v>
+        <v>121402402</v>
       </c>
       <c r="B68" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8255,19 +8255,19 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695869</v>
+        <v>695942</v>
       </c>
       <c r="R68" t="n">
-        <v>6603281</v>
+        <v>6603075</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121402352</v>
+        <v>121404569</v>
       </c>
       <c r="B69" t="n">
-        <v>57372</v>
+        <v>4776</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8338,43 +8338,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696013</v>
+        <v>695858</v>
       </c>
       <c r="R69" t="n">
-        <v>6603120</v>
+        <v>6603299</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121402404</v>
+        <v>121404209</v>
       </c>
       <c r="B70" t="n">
-        <v>5172</v>
+        <v>94515</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8449,39 +8449,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>2809</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695942</v>
+        <v>695935</v>
       </c>
       <c r="R70" t="n">
-        <v>6603075</v>
+        <v>6603415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8540,10 +8535,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121404898</v>
+        <v>121402734</v>
       </c>
       <c r="B71" t="n">
-        <v>8424</v>
+        <v>57373</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8552,43 +8547,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696024</v>
+        <v>696145</v>
       </c>
       <c r="R71" t="n">
-        <v>6603210</v>
+        <v>6603212</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8618,9 +8613,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8635,22 +8640,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121404815</v>
+        <v>121404366</v>
       </c>
       <c r="B72" t="n">
-        <v>94507</v>
+        <v>90728</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8659,25 +8664,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8687,10 +8692,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695864</v>
+        <v>695857</v>
       </c>
       <c r="R72" t="n">
-        <v>6603266</v>
+        <v>6603366</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8749,10 +8754,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121402809</v>
+        <v>121403961</v>
       </c>
       <c r="B73" t="n">
-        <v>57372</v>
+        <v>79697</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8765,39 +8770,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696135</v>
+        <v>695886</v>
       </c>
       <c r="R73" t="n">
-        <v>6603162</v>
+        <v>6603243</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8827,9 +8827,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8844,22 +8859,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121405386</v>
+        <v>121402404</v>
       </c>
       <c r="B74" t="n">
-        <v>90685</v>
+        <v>5173</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8872,34 +8887,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696099</v>
+        <v>695942</v>
       </c>
       <c r="R74" t="n">
-        <v>6603163</v>
+        <v>6603075</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8958,10 +8978,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121402709</v>
+        <v>121404545</v>
       </c>
       <c r="B75" t="n">
-        <v>57372</v>
+        <v>8436</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8970,43 +8990,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696025</v>
+        <v>695870</v>
       </c>
       <c r="R75" t="n">
-        <v>6603166</v>
+        <v>6603295</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9065,10 +9080,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121404569</v>
+        <v>121402355</v>
       </c>
       <c r="B76" t="n">
-        <v>4775</v>
+        <v>5193</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9081,21 +9096,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9110,10 +9125,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695858</v>
+        <v>696001</v>
       </c>
       <c r="R76" t="n">
-        <v>6603299</v>
+        <v>6603109</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9172,10 +9187,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404366</v>
+        <v>121404539</v>
       </c>
       <c r="B77" t="n">
-        <v>90720</v>
+        <v>57373</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9188,34 +9203,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695857</v>
+        <v>695869</v>
       </c>
       <c r="R77" t="n">
-        <v>6603366</v>
+        <v>6603281</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9274,10 +9294,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402734</v>
+        <v>121402709</v>
       </c>
       <c r="B78" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9310,19 +9330,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696145</v>
+        <v>696025</v>
       </c>
       <c r="R78" t="n">
-        <v>6603212</v>
+        <v>6603166</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9352,19 +9372,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9379,22 +9389,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121402355</v>
+        <v>121404815</v>
       </c>
       <c r="B79" t="n">
-        <v>5192</v>
+        <v>94515</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9407,39 +9417,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>105930</v>
+        <v>2809</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696001</v>
+        <v>695864</v>
       </c>
       <c r="R79" t="n">
-        <v>6603109</v>
+        <v>6603266</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9498,10 +9503,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121405694</v>
+        <v>121404249</v>
       </c>
       <c r="B80" t="n">
-        <v>98105</v>
+        <v>57373</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9510,52 +9515,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695999</v>
+        <v>695896</v>
       </c>
       <c r="R80" t="n">
-        <v>6603117</v>
+        <v>6603382</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9585,24 +9581,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9617,22 +9598,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121402388</v>
+        <v>121404558</v>
       </c>
       <c r="B81" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9665,19 +9646,19 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695971</v>
+        <v>695865</v>
       </c>
       <c r="R81" t="n">
-        <v>6603090</v>
+        <v>6603318</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9707,9 +9688,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9724,22 +9715,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121404209</v>
+        <v>121402352</v>
       </c>
       <c r="B82" t="n">
-        <v>94507</v>
+        <v>57373</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9748,38 +9739,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695935</v>
+        <v>696013</v>
       </c>
       <c r="R82" t="n">
-        <v>6603415</v>
+        <v>6603120</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9838,10 +9834,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121404249</v>
+        <v>121402809</v>
       </c>
       <c r="B83" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9879,14 +9875,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695896</v>
+        <v>696135</v>
       </c>
       <c r="R83" t="n">
-        <v>6603382</v>
+        <v>6603162</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9945,10 +9941,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404558</v>
+        <v>121404898</v>
       </c>
       <c r="B84" t="n">
-        <v>57372</v>
+        <v>8425</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9957,43 +9953,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695865</v>
+        <v>696024</v>
       </c>
       <c r="R84" t="n">
-        <v>6603318</v>
+        <v>6603210</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10023,19 +10019,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10050,22 +10036,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404293</v>
+        <v>121405694</v>
       </c>
       <c r="B85" t="n">
-        <v>5172</v>
+        <v>98113</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10074,43 +10060,52 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695856</v>
+        <v>695999</v>
       </c>
       <c r="R85" t="n">
-        <v>6603367</v>
+        <v>6603117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,9 +10135,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10157,22 +10167,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121403961</v>
+        <v>121405386</v>
       </c>
       <c r="B86" t="n">
-        <v>79690</v>
+        <v>90693</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10181,38 +10191,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695886</v>
+        <v>696099</v>
       </c>
       <c r="R86" t="n">
-        <v>6603243</v>
+        <v>6603163</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10242,24 +10252,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10274,22 +10269,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121404545</v>
+        <v>121402388</v>
       </c>
       <c r="B87" t="n">
-        <v>8435</v>
+        <v>57373</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10298,38 +10293,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695870</v>
+        <v>695971</v>
       </c>
       <c r="R87" t="n">
-        <v>6603295</v>
+        <v>6603090</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10388,10 +10388,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121402402</v>
+        <v>121404293</v>
       </c>
       <c r="B88" t="n">
-        <v>57372</v>
+        <v>5173</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10400,43 +10400,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695942</v>
+        <v>695856</v>
       </c>
       <c r="R88" t="n">
-        <v>6603075</v>
+        <v>6603367</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8754,10 +8754,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121403961</v>
+        <v>121402404</v>
       </c>
       <c r="B73" t="n">
-        <v>79697</v>
+        <v>5173</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8766,38 +8766,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695886</v>
+        <v>695942</v>
       </c>
       <c r="R73" t="n">
-        <v>6603243</v>
+        <v>6603075</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8827,24 +8832,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8859,22 +8849,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121402404</v>
+        <v>121403961</v>
       </c>
       <c r="B74" t="n">
-        <v>5173</v>
+        <v>79697</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8883,43 +8873,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695942</v>
+        <v>695886</v>
       </c>
       <c r="R74" t="n">
-        <v>6603075</v>
+        <v>6603243</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8949,9 +8934,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8966,22 +8966,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121404545</v>
+        <v>121404539</v>
       </c>
       <c r="B75" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8990,38 +8990,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695870</v>
+        <v>695869</v>
       </c>
       <c r="R75" t="n">
-        <v>6603295</v>
+        <v>6603281</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9080,10 +9085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121402355</v>
+        <v>121402709</v>
       </c>
       <c r="B76" t="n">
-        <v>5193</v>
+        <v>57373</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9092,20 +9097,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9116,19 +9121,19 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696001</v>
+        <v>696025</v>
       </c>
       <c r="R76" t="n">
-        <v>6603109</v>
+        <v>6603166</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9187,10 +9192,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121404539</v>
+        <v>121404545</v>
       </c>
       <c r="B77" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9199,43 +9204,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695869</v>
+        <v>695870</v>
       </c>
       <c r="R77" t="n">
-        <v>6603281</v>
+        <v>6603295</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9294,10 +9294,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121402709</v>
+        <v>121402355</v>
       </c>
       <c r="B78" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9306,20 +9306,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9330,19 +9330,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Naturskog norr om Gallboda , Naturskog norr om Gallboda , Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696025</v>
+        <v>696001</v>
       </c>
       <c r="R78" t="n">
-        <v>6603166</v>
+        <v>6603109</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9941,10 +9941,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121404898</v>
+        <v>121405386</v>
       </c>
       <c r="B84" t="n">
-        <v>8425</v>
+        <v>90693</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9957,39 +9957,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696024</v>
+        <v>696099</v>
       </c>
       <c r="R84" t="n">
-        <v>6603210</v>
+        <v>6603163</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10048,10 +10043,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121405694</v>
+        <v>121404898</v>
       </c>
       <c r="B85" t="n">
-        <v>98113</v>
+        <v>8425</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10060,52 +10055,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695999</v>
+        <v>696024</v>
       </c>
       <c r="R85" t="n">
-        <v>6603117</v>
+        <v>6603210</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10135,24 +10121,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10167,22 +10138,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121405386</v>
+        <v>121405694</v>
       </c>
       <c r="B86" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10191,38 +10162,52 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>696099</v>
+        <v>695999</v>
       </c>
       <c r="R86" t="n">
-        <v>6603163</v>
+        <v>6603117</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10252,9 +10237,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10269,12 +10269,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -8754,10 +8754,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121402404</v>
+        <v>121403961</v>
       </c>
       <c r="B73" t="n">
-        <v>5173</v>
+        <v>79697</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8766,43 +8766,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695942</v>
+        <v>695886</v>
       </c>
       <c r="R73" t="n">
-        <v>6603075</v>
+        <v>6603243</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8832,9 +8827,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8849,22 +8859,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121403961</v>
+        <v>121402404</v>
       </c>
       <c r="B74" t="n">
-        <v>79697</v>
+        <v>5173</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8873,38 +8883,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695886</v>
+        <v>695942</v>
       </c>
       <c r="R74" t="n">
-        <v>6603243</v>
+        <v>6603075</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8934,24 +8949,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla aspar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8966,12 +8966,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9941,10 +9941,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121405386</v>
+        <v>121404898</v>
       </c>
       <c r="B84" t="n">
-        <v>90693</v>
+        <v>8425</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9957,34 +9957,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696099</v>
+        <v>696024</v>
       </c>
       <c r="R84" t="n">
-        <v>6603163</v>
+        <v>6603210</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,10 +10048,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121404898</v>
+        <v>121405694</v>
       </c>
       <c r="B85" t="n">
-        <v>8425</v>
+        <v>98113</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10055,43 +10060,52 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tärnan, Tärnan, Upl</t>
+          <t>Torpängen, Torpängen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696024</v>
+        <v>695999</v>
       </c>
       <c r="R85" t="n">
-        <v>6603210</v>
+        <v>6603117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10121,9 +10135,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10138,22 +10167,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121405694</v>
+        <v>121405386</v>
       </c>
       <c r="B86" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10162,52 +10191,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torpängen, Torpängen, Upl</t>
+          <t>Tärnan, Tärnan, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695999</v>
+        <v>696099</v>
       </c>
       <c r="R86" t="n">
-        <v>6603117</v>
+        <v>6603163</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10237,24 +10252,9 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer på en bergkulle som sluttar åt NV strax intill  (öster om) en liten sump och en äldre tall.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10269,12 +10269,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 46651-2024 artfynd.xlsx
+++ b/artfynd/A 46651-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090573</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090597</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785543</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785338</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785370</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114942675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114942988</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943271</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115041655</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090372</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121091186</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121091232</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095265</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404366</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2363,6 +2443,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404306</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2464,6 +2549,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785431</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2576,6 +2666,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943342</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2697,6 +2792,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943736</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2804,6 +2904,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121092954</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2916,6 +3021,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090764</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3013,6 +3123,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090765</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,6 +3225,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404209</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404815</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3304,6 +3429,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404846</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3401,6 +3531,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121093973</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3509,6 +3644,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406893</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3606,6 +3746,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404492</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3743,6 +3888,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114941998</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3855,6 +4005,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944138</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3952,6 +4107,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404405</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4059,6 +4219,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404478</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4156,6 +4321,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405386</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4268,6 +4438,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944111</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4380,6 +4555,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944180</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4487,6 +4667,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121091126</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4594,6 +4779,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121091319</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4695,6 +4885,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404155</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4796,6 +4991,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404158</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4893,6 +5093,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090442</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5020,6 +5225,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090488</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5157,6 +5367,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115040924</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5269,6 +5484,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121403961</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5372,6 +5592,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113400782</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5475,6 +5700,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113401130</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5592,6 +5822,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114942064</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5713,6 +5948,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115041598</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5829,6 +6069,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115952075</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5941,6 +6186,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121093800</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6043,6 +6293,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095556</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6145,6 +6400,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402352</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6247,6 +6507,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402388</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6349,6 +6614,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402402</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6451,6 +6721,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402709</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6563,6 +6838,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402734</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6665,6 +6945,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402809</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6767,6 +7052,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402936</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6869,6 +7159,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404249</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6971,6 +7266,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404539</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7083,6 +7383,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404558</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7200,6 +7505,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943459</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7317,6 +7627,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943970</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7429,6 +7744,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944965</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7541,6 +7861,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114945342</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7657,6 +7982,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115041049</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7769,6 +8099,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121093817</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7881,6 +8216,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121094438</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7993,6 +8333,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121094501</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8105,6 +8450,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095299</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8207,6 +8557,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402361</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8309,6 +8664,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402404</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8411,6 +8771,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404293</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8513,6 +8878,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404569</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8620,6 +8990,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113400587</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8737,6 +9112,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114942139</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8849,6 +9229,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121093815</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8961,6 +9346,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095510</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9073,6 +9463,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095837</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9175,6 +9570,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402355</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9287,6 +9687,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944951</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9403,6 +9808,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115041348</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9519,6 +9929,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115041615</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9616,6 +10031,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404545</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9723,6 +10143,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113400376</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9830,6 +10255,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113400795</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9944,6 +10374,11 @@
       <c r="AY87" t="inlineStr">
         <is>
           <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115041372</t>
         </is>
       </c>
     </row>
@@ -10053,6 +10488,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121091050</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10155,6 +10595,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404898</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10253,6 +10698,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113401216</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10351,6 +10801,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113415714</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10477,6 +10932,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405694</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10589,6 +11049,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114945730</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10699,6 +11164,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124291875</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10796,6 +11266,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090637</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10893,6 +11368,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090910</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10990,6 +11470,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121091204</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11087,6 +11572,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121093980</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11184,8 +11674,113 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>